--- a/attendance/勤怠管理_休暇調整シート.xlsx
+++ b/attendance/勤怠管理_休暇調整シート.xlsx
@@ -21,13 +21,13 @@
     <definedName name="MIN_ALL">設定!$C$14</definedName>
     <definedName name="MIN_FT">設定!$C$15</definedName>
     <definedName name="SYM_TBL">設定!$B$30:$D$38</definedName>
-    <definedName name="LOG_NAME">休暇申請!$C$5:$C$204</definedName>
-    <definedName name="LOG_DATE">休暇申請!$D$5:$D$204</definedName>
-    <definedName name="LOG_SYM">休暇申請!$E$5:$E$204</definedName>
-    <definedName name="LOG_STATE">休暇申請!$G$5:$G$204</definedName>
-    <definedName name="KEY_A">休暇申請!$L$5:$L$204</definedName>
-    <definedName name="KEY_P">休暇申請!$M$5:$M$204</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'休暇申請'!$B$4:$M$204</definedName>
+    <definedName name="LOG_NAME">休暇申請!$C$5:$C$124</definedName>
+    <definedName name="LOG_DATE">休暇申請!$D$5:$D$124</definedName>
+    <definedName name="LOG_SYM">休暇申請!$E$5:$E$124</definedName>
+    <definedName name="LOG_STATE">休暇申請!$G$5:$G$124</definedName>
+    <definedName name="KEY_A">休暇申請!$L$5:$L$124</definedName>
+    <definedName name="KEY_P">休暇申請!$M$5:$M$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'休暇申請'!$B$4:$M$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -267,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -347,6 +347,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -372,7 +380,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -461,6 +469,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F39C12"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF6DD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4875,7 +4890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M204"/>
+  <dimension ref="B1:M124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5008,24 +5023,24 @@
           <t>正社員B</t>
         </is>
       </c>
-      <c r="I5" s="22">
-        <f t="shared" ref="I5:I204" si="0">IF(D5="","",COUNTIFS(LOG_DATE,D5,LOG_STATE,"承認")+COUNTIFS(LOG_DATE,D5,LOG_STATE,"申請中")-IF(G5="却下",0,1))</f>
-        <v/>
-      </c>
-      <c r="J5" s="22">
-        <f t="shared" ref="J5:J204" si="1">IF(D5="","",IFERROR(SUMPRODUCT((INDEX(STAFF_DAYS,0,WEEKDAY(D5,2))="○")*1)-I5-IF(G5="却下",0,1),"日付を確認"))</f>
-        <v/>
-      </c>
-      <c r="K5" s="27">
-        <f t="shared" ref="K5:K204" si="2">IF(D5="","",IFERROR(IF(OR(INDEX(BIZ_DAYS,WEEKDAY(D5,2))="×",COUNTIF(HOLIDAYS,D5)&gt;0),"休業日",IF(J5&lt;MIN_ALL,"要確認","OK")),"日付を確認"))</f>
-        <v/>
-      </c>
-      <c r="L5" s="29">
-        <f t="shared" ref="L5:L204" si="3">IF(AND(G5="承認",C5&lt;&gt;"",D5&lt;&gt;""),C5&amp;"|"&amp;TEXT(D5,"yyyymmdd"),"")</f>
-        <v/>
-      </c>
-      <c r="M5" s="29">
-        <f t="shared" ref="M5:M204" si="4">IF(AND(G5="申請中",C5&lt;&gt;"",D5&lt;&gt;""),C5&amp;"|"&amp;TEXT(D5,"yyyymmdd"),"")</f>
+      <c r="I5" s="35">
+        <f t="shared" ref="I5:I124" si="0">IF(D5="","",COUNTIFS(LOG_DATE,D5,LOG_STATE,"承認")+COUNTIFS(LOG_DATE,D5,LOG_STATE,"申請中")-IF(G5="却下",0,1))</f>
+        <v/>
+      </c>
+      <c r="J5" s="35">
+        <f t="shared" ref="J5:J124" si="1">IF(D5="","",IFERROR(SUMPRODUCT((INDEX(STAFF_DAYS,0,WEEKDAY(D5,2))="○")*1)-I5-IF(G5="却下",0,1),"日付を確認"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="36">
+        <f t="shared" ref="K5:K124" si="2">IF(D5="","",IFERROR(IF(OR(INDEX(BIZ_DAYS,WEEKDAY(D5,2))="×",COUNTIF(HOLIDAYS,D5)&gt;0),"休業日",IF(J5&lt;MIN_ALL,"要確認","OK")),"日付を確認"))</f>
+        <v/>
+      </c>
+      <c r="L5" s="37">
+        <f t="shared" ref="L5:L124" si="3">IF(AND(G5="承認",C5&lt;&gt;"",D5&lt;&gt;""),C5&amp;"|"&amp;TEXT(D5,"yyyymmdd"),"")</f>
+        <v/>
+      </c>
+      <c r="M5" s="37">
+        <f t="shared" ref="M5:M124" si="4">IF(AND(G5="申請中",C5&lt;&gt;"",D5&lt;&gt;""),C5&amp;"|"&amp;TEXT(D5,"yyyymmdd"),"")</f>
         <v/>
       </c>
     </row>
@@ -5057,23 +5072,23 @@
         </is>
       </c>
       <c r="H6" s="33" t="inlineStr"/>
-      <c r="I6" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J6" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K6" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L6" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M6" s="29">
+      <c r="I6" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J6" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K6" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L6" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M6" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -5110,23 +5125,23 @@
           <t>正社員A</t>
         </is>
       </c>
-      <c r="I7" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L7" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M7" s="29">
+      <c r="I7" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J7" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K7" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L7" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M7" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -5159,5743 +5174,2848 @@
         </is>
       </c>
       <c r="H8" s="33" t="inlineStr"/>
-      <c r="I8" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L8" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M8" s="29">
+      <c r="I8" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J8" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K8" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L8" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M8" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="32" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="32" t="n"/>
-      <c r="E9" s="34" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="34" t="n"/>
-      <c r="H9" s="33" t="n"/>
-      <c r="I9" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L9" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M9" s="29">
+      <c r="B9" s="38" t="n"/>
+      <c r="D9" s="38" t="n"/>
+      <c r="I9" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J9" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K9" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L9" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M9" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="32" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="32" t="n"/>
-      <c r="E10" s="34" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="34" t="n"/>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L10" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M10" s="29">
+      <c r="B10" s="38" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="I10" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J10" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K10" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L10" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M10" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="32" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="32" t="n"/>
-      <c r="E11" s="34" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="34" t="n"/>
-      <c r="H11" s="33" t="n"/>
-      <c r="I11" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L11" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M11" s="29">
+      <c r="B11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="I11" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J11" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K11" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L11" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M11" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="32" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="32" t="n"/>
-      <c r="E12" s="34" t="n"/>
-      <c r="F12" s="33" t="n"/>
-      <c r="G12" s="34" t="n"/>
-      <c r="H12" s="33" t="n"/>
-      <c r="I12" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L12" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M12" s="29">
+      <c r="B12" s="38" t="n"/>
+      <c r="D12" s="38" t="n"/>
+      <c r="I12" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J12" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K12" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L12" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M12" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="32" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="32" t="n"/>
-      <c r="E13" s="34" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="34" t="n"/>
-      <c r="H13" s="33" t="n"/>
-      <c r="I13" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L13" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M13" s="29">
+      <c r="B13" s="38" t="n"/>
+      <c r="D13" s="38" t="n"/>
+      <c r="I13" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J13" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K13" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L13" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M13" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="32" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="34" t="n"/>
-      <c r="F14" s="33" t="n"/>
-      <c r="G14" s="34" t="n"/>
-      <c r="H14" s="33" t="n"/>
-      <c r="I14" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L14" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M14" s="29">
+      <c r="B14" s="38" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="I14" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J14" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K14" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L14" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M14" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="32" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="34" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="34" t="n"/>
-      <c r="H15" s="33" t="n"/>
-      <c r="I15" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L15" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M15" s="29">
+      <c r="B15" s="38" t="n"/>
+      <c r="D15" s="38" t="n"/>
+      <c r="I15" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J15" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K15" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L15" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M15" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="32" t="n"/>
-      <c r="C16" s="33" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="34" t="n"/>
-      <c r="F16" s="33" t="n"/>
-      <c r="G16" s="34" t="n"/>
-      <c r="H16" s="33" t="n"/>
-      <c r="I16" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L16" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M16" s="29">
+      <c r="B16" s="38" t="n"/>
+      <c r="D16" s="38" t="n"/>
+      <c r="I16" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J16" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K16" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L16" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M16" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="n"/>
-      <c r="C17" s="33" t="n"/>
-      <c r="D17" s="32" t="n"/>
-      <c r="E17" s="34" t="n"/>
-      <c r="F17" s="33" t="n"/>
-      <c r="G17" s="34" t="n"/>
-      <c r="H17" s="33" t="n"/>
-      <c r="I17" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L17" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M17" s="29">
+      <c r="B17" s="38" t="n"/>
+      <c r="D17" s="38" t="n"/>
+      <c r="I17" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J17" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K17" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L17" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M17" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="32" t="n"/>
-      <c r="C18" s="33" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="34" t="n"/>
-      <c r="F18" s="33" t="n"/>
-      <c r="G18" s="34" t="n"/>
-      <c r="H18" s="33" t="n"/>
-      <c r="I18" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L18" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M18" s="29">
+      <c r="B18" s="38" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="I18" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J18" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K18" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L18" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M18" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="33" t="n"/>
-      <c r="D19" s="32" t="n"/>
-      <c r="E19" s="34" t="n"/>
-      <c r="F19" s="33" t="n"/>
-      <c r="G19" s="34" t="n"/>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L19" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M19" s="29">
+      <c r="B19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="I19" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J19" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K19" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L19" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M19" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="32" t="n"/>
-      <c r="C20" s="33" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="34" t="n"/>
-      <c r="F20" s="33" t="n"/>
-      <c r="G20" s="34" t="n"/>
-      <c r="H20" s="33" t="n"/>
-      <c r="I20" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L20" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M20" s="29">
+      <c r="B20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="I20" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J20" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K20" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L20" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M20" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="32" t="n"/>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="33" t="n"/>
-      <c r="G21" s="34" t="n"/>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L21" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M21" s="29">
+      <c r="B21" s="38" t="n"/>
+      <c r="D21" s="38" t="n"/>
+      <c r="I21" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J21" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K21" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L21" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M21" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="32" t="n"/>
-      <c r="C22" s="33" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="34" t="n"/>
-      <c r="F22" s="33" t="n"/>
-      <c r="G22" s="34" t="n"/>
-      <c r="H22" s="33" t="n"/>
-      <c r="I22" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L22" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M22" s="29">
+      <c r="B22" s="38" t="n"/>
+      <c r="D22" s="38" t="n"/>
+      <c r="I22" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J22" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K22" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L22" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M22" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="33" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="34" t="n"/>
-      <c r="F23" s="33" t="n"/>
-      <c r="G23" s="34" t="n"/>
-      <c r="H23" s="33" t="n"/>
-      <c r="I23" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L23" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M23" s="29">
+      <c r="B23" s="38" t="n"/>
+      <c r="D23" s="38" t="n"/>
+      <c r="I23" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J23" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K23" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L23" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M23" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="33" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="33" t="n"/>
-      <c r="G24" s="34" t="n"/>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L24" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M24" s="29">
+      <c r="B24" s="38" t="n"/>
+      <c r="D24" s="38" t="n"/>
+      <c r="I24" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J24" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K24" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L24" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M24" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="32" t="n"/>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="32" t="n"/>
-      <c r="E25" s="34" t="n"/>
-      <c r="F25" s="33" t="n"/>
-      <c r="G25" s="34" t="n"/>
-      <c r="H25" s="33" t="n"/>
-      <c r="I25" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L25" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M25" s="29">
+      <c r="B25" s="38" t="n"/>
+      <c r="D25" s="38" t="n"/>
+      <c r="I25" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J25" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K25" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L25" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M25" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="32" t="n"/>
-      <c r="C26" s="33" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="33" t="n"/>
-      <c r="G26" s="34" t="n"/>
-      <c r="H26" s="33" t="n"/>
-      <c r="I26" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L26" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M26" s="29">
+      <c r="B26" s="38" t="n"/>
+      <c r="D26" s="38" t="n"/>
+      <c r="I26" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J26" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K26" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L26" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M26" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="33" t="n"/>
-      <c r="G27" s="34" t="n"/>
-      <c r="H27" s="33" t="n"/>
-      <c r="I27" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L27" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M27" s="29">
+      <c r="B27" s="38" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="I27" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J27" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K27" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L27" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M27" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="32" t="n"/>
-      <c r="C28" s="33" t="n"/>
-      <c r="D28" s="32" t="n"/>
-      <c r="E28" s="34" t="n"/>
-      <c r="F28" s="33" t="n"/>
-      <c r="G28" s="34" t="n"/>
-      <c r="H28" s="33" t="n"/>
-      <c r="I28" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L28" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M28" s="29">
+      <c r="B28" s="38" t="n"/>
+      <c r="D28" s="38" t="n"/>
+      <c r="I28" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J28" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K28" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L28" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M28" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="32" t="n"/>
-      <c r="C29" s="33" t="n"/>
-      <c r="D29" s="32" t="n"/>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="33" t="n"/>
-      <c r="G29" s="34" t="n"/>
-      <c r="H29" s="33" t="n"/>
-      <c r="I29" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L29" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M29" s="29">
+      <c r="B29" s="38" t="n"/>
+      <c r="D29" s="38" t="n"/>
+      <c r="I29" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J29" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K29" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L29" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M29" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="32" t="n"/>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="33" t="n"/>
-      <c r="G30" s="34" t="n"/>
-      <c r="H30" s="33" t="n"/>
-      <c r="I30" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L30" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M30" s="29">
+      <c r="B30" s="38" t="n"/>
+      <c r="D30" s="38" t="n"/>
+      <c r="I30" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J30" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K30" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L30" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M30" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="32" t="n"/>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="32" t="n"/>
-      <c r="E31" s="34" t="n"/>
-      <c r="F31" s="33" t="n"/>
-      <c r="G31" s="34" t="n"/>
-      <c r="H31" s="33" t="n"/>
-      <c r="I31" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L31" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M31" s="29">
+      <c r="B31" s="38" t="n"/>
+      <c r="D31" s="38" t="n"/>
+      <c r="I31" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J31" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K31" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L31" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M31" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="32" t="n"/>
-      <c r="C32" s="33" t="n"/>
-      <c r="D32" s="32" t="n"/>
-      <c r="E32" s="34" t="n"/>
-      <c r="F32" s="33" t="n"/>
-      <c r="G32" s="34" t="n"/>
-      <c r="H32" s="33" t="n"/>
-      <c r="I32" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L32" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M32" s="29">
+      <c r="B32" s="38" t="n"/>
+      <c r="D32" s="38" t="n"/>
+      <c r="I32" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J32" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K32" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L32" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M32" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="32" t="n"/>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="32" t="n"/>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="33" t="n"/>
-      <c r="G33" s="34" t="n"/>
-      <c r="H33" s="33" t="n"/>
-      <c r="I33" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L33" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M33" s="29">
+      <c r="B33" s="38" t="n"/>
+      <c r="D33" s="38" t="n"/>
+      <c r="I33" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J33" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K33" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L33" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M33" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="32" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="32" t="n"/>
-      <c r="E34" s="34" t="n"/>
-      <c r="F34" s="33" t="n"/>
-      <c r="G34" s="34" t="n"/>
-      <c r="H34" s="33" t="n"/>
-      <c r="I34" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L34" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M34" s="29">
+      <c r="B34" s="38" t="n"/>
+      <c r="D34" s="38" t="n"/>
+      <c r="I34" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J34" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K34" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L34" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M34" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="32" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="32" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="33" t="n"/>
-      <c r="G35" s="34" t="n"/>
-      <c r="H35" s="33" t="n"/>
-      <c r="I35" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L35" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M35" s="29">
+      <c r="B35" s="38" t="n"/>
+      <c r="D35" s="38" t="n"/>
+      <c r="I35" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J35" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K35" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L35" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M35" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="32" t="n"/>
-      <c r="C36" s="33" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="33" t="n"/>
-      <c r="G36" s="34" t="n"/>
-      <c r="H36" s="33" t="n"/>
-      <c r="I36" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L36" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M36" s="29">
+      <c r="B36" s="38" t="n"/>
+      <c r="D36" s="38" t="n"/>
+      <c r="I36" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J36" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K36" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L36" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M36" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="32" t="n"/>
-      <c r="C37" s="33" t="n"/>
-      <c r="D37" s="32" t="n"/>
-      <c r="E37" s="34" t="n"/>
-      <c r="F37" s="33" t="n"/>
-      <c r="G37" s="34" t="n"/>
-      <c r="H37" s="33" t="n"/>
-      <c r="I37" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L37" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M37" s="29">
+      <c r="B37" s="38" t="n"/>
+      <c r="D37" s="38" t="n"/>
+      <c r="I37" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J37" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K37" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L37" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M37" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="33" t="n"/>
-      <c r="D38" s="32" t="n"/>
-      <c r="E38" s="34" t="n"/>
-      <c r="F38" s="33" t="n"/>
-      <c r="G38" s="34" t="n"/>
-      <c r="H38" s="33" t="n"/>
-      <c r="I38" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L38" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M38" s="29">
+      <c r="B38" s="38" t="n"/>
+      <c r="D38" s="38" t="n"/>
+      <c r="I38" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J38" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K38" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L38" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M38" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="32" t="n"/>
-      <c r="C39" s="33" t="n"/>
-      <c r="D39" s="32" t="n"/>
-      <c r="E39" s="34" t="n"/>
-      <c r="F39" s="33" t="n"/>
-      <c r="G39" s="34" t="n"/>
-      <c r="H39" s="33" t="n"/>
-      <c r="I39" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L39" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M39" s="29">
+      <c r="B39" s="38" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="I39" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J39" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K39" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L39" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M39" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="33" t="n"/>
-      <c r="D40" s="32" t="n"/>
-      <c r="E40" s="34" t="n"/>
-      <c r="F40" s="33" t="n"/>
-      <c r="G40" s="34" t="n"/>
-      <c r="H40" s="33" t="n"/>
-      <c r="I40" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L40" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M40" s="29">
+      <c r="B40" s="38" t="n"/>
+      <c r="D40" s="38" t="n"/>
+      <c r="I40" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J40" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K40" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L40" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M40" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="32" t="n"/>
-      <c r="C41" s="33" t="n"/>
-      <c r="D41" s="32" t="n"/>
-      <c r="E41" s="34" t="n"/>
-      <c r="F41" s="33" t="n"/>
-      <c r="G41" s="34" t="n"/>
-      <c r="H41" s="33" t="n"/>
-      <c r="I41" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L41" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M41" s="29">
+      <c r="B41" s="38" t="n"/>
+      <c r="D41" s="38" t="n"/>
+      <c r="I41" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J41" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K41" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L41" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M41" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="32" t="n"/>
-      <c r="C42" s="33" t="n"/>
-      <c r="D42" s="32" t="n"/>
-      <c r="E42" s="34" t="n"/>
-      <c r="F42" s="33" t="n"/>
-      <c r="G42" s="34" t="n"/>
-      <c r="H42" s="33" t="n"/>
-      <c r="I42" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L42" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M42" s="29">
+      <c r="B42" s="38" t="n"/>
+      <c r="D42" s="38" t="n"/>
+      <c r="I42" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J42" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K42" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L42" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M42" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="32" t="n"/>
-      <c r="C43" s="33" t="n"/>
-      <c r="D43" s="32" t="n"/>
-      <c r="E43" s="34" t="n"/>
-      <c r="F43" s="33" t="n"/>
-      <c r="G43" s="34" t="n"/>
-      <c r="H43" s="33" t="n"/>
-      <c r="I43" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L43" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M43" s="29">
+      <c r="B43" s="38" t="n"/>
+      <c r="D43" s="38" t="n"/>
+      <c r="I43" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J43" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K43" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L43" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M43" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="32" t="n"/>
-      <c r="C44" s="33" t="n"/>
-      <c r="D44" s="32" t="n"/>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="33" t="n"/>
-      <c r="G44" s="34" t="n"/>
-      <c r="H44" s="33" t="n"/>
-      <c r="I44" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L44" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M44" s="29">
+      <c r="B44" s="38" t="n"/>
+      <c r="D44" s="38" t="n"/>
+      <c r="I44" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J44" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K44" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L44" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M44" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="32" t="n"/>
-      <c r="C45" s="33" t="n"/>
-      <c r="D45" s="32" t="n"/>
-      <c r="E45" s="34" t="n"/>
-      <c r="F45" s="33" t="n"/>
-      <c r="G45" s="34" t="n"/>
-      <c r="H45" s="33" t="n"/>
-      <c r="I45" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L45" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M45" s="29">
+      <c r="B45" s="38" t="n"/>
+      <c r="D45" s="38" t="n"/>
+      <c r="I45" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J45" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K45" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L45" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M45" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="32" t="n"/>
-      <c r="C46" s="33" t="n"/>
-      <c r="D46" s="32" t="n"/>
-      <c r="E46" s="34" t="n"/>
-      <c r="F46" s="33" t="n"/>
-      <c r="G46" s="34" t="n"/>
-      <c r="H46" s="33" t="n"/>
-      <c r="I46" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L46" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M46" s="29">
+      <c r="B46" s="38" t="n"/>
+      <c r="D46" s="38" t="n"/>
+      <c r="I46" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J46" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K46" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L46" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M46" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="32" t="n"/>
-      <c r="C47" s="33" t="n"/>
-      <c r="D47" s="32" t="n"/>
-      <c r="E47" s="34" t="n"/>
-      <c r="F47" s="33" t="n"/>
-      <c r="G47" s="34" t="n"/>
-      <c r="H47" s="33" t="n"/>
-      <c r="I47" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L47" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M47" s="29">
+      <c r="B47" s="38" t="n"/>
+      <c r="D47" s="38" t="n"/>
+      <c r="I47" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J47" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K47" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L47" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M47" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="32" t="n"/>
-      <c r="C48" s="33" t="n"/>
-      <c r="D48" s="32" t="n"/>
-      <c r="E48" s="34" t="n"/>
-      <c r="F48" s="33" t="n"/>
-      <c r="G48" s="34" t="n"/>
-      <c r="H48" s="33" t="n"/>
-      <c r="I48" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L48" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M48" s="29">
+      <c r="B48" s="38" t="n"/>
+      <c r="D48" s="38" t="n"/>
+      <c r="I48" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J48" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K48" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L48" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M48" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="32" t="n"/>
-      <c r="C49" s="33" t="n"/>
-      <c r="D49" s="32" t="n"/>
-      <c r="E49" s="34" t="n"/>
-      <c r="F49" s="33" t="n"/>
-      <c r="G49" s="34" t="n"/>
-      <c r="H49" s="33" t="n"/>
-      <c r="I49" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L49" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M49" s="29">
+      <c r="B49" s="38" t="n"/>
+      <c r="D49" s="38" t="n"/>
+      <c r="I49" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J49" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K49" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L49" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M49" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="32" t="n"/>
-      <c r="C50" s="33" t="n"/>
-      <c r="D50" s="32" t="n"/>
-      <c r="E50" s="34" t="n"/>
-      <c r="F50" s="33" t="n"/>
-      <c r="G50" s="34" t="n"/>
-      <c r="H50" s="33" t="n"/>
-      <c r="I50" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L50" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M50" s="29">
+      <c r="B50" s="38" t="n"/>
+      <c r="D50" s="38" t="n"/>
+      <c r="I50" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J50" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K50" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L50" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M50" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="32" t="n"/>
-      <c r="C51" s="33" t="n"/>
-      <c r="D51" s="32" t="n"/>
-      <c r="E51" s="34" t="n"/>
-      <c r="F51" s="33" t="n"/>
-      <c r="G51" s="34" t="n"/>
-      <c r="H51" s="33" t="n"/>
-      <c r="I51" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L51" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M51" s="29">
+      <c r="B51" s="38" t="n"/>
+      <c r="D51" s="38" t="n"/>
+      <c r="I51" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J51" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K51" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L51" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M51" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="32" t="n"/>
-      <c r="C52" s="33" t="n"/>
-      <c r="D52" s="32" t="n"/>
-      <c r="E52" s="34" t="n"/>
-      <c r="F52" s="33" t="n"/>
-      <c r="G52" s="34" t="n"/>
-      <c r="H52" s="33" t="n"/>
-      <c r="I52" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L52" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M52" s="29">
+      <c r="B52" s="38" t="n"/>
+      <c r="D52" s="38" t="n"/>
+      <c r="I52" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J52" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K52" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L52" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M52" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="32" t="n"/>
-      <c r="C53" s="33" t="n"/>
-      <c r="D53" s="32" t="n"/>
-      <c r="E53" s="34" t="n"/>
-      <c r="F53" s="33" t="n"/>
-      <c r="G53" s="34" t="n"/>
-      <c r="H53" s="33" t="n"/>
-      <c r="I53" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L53" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M53" s="29">
+      <c r="B53" s="38" t="n"/>
+      <c r="D53" s="38" t="n"/>
+      <c r="I53" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J53" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K53" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L53" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M53" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="32" t="n"/>
-      <c r="C54" s="33" t="n"/>
-      <c r="D54" s="32" t="n"/>
-      <c r="E54" s="34" t="n"/>
-      <c r="F54" s="33" t="n"/>
-      <c r="G54" s="34" t="n"/>
-      <c r="H54" s="33" t="n"/>
-      <c r="I54" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L54" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M54" s="29">
+      <c r="B54" s="38" t="n"/>
+      <c r="D54" s="38" t="n"/>
+      <c r="I54" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J54" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K54" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L54" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M54" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="32" t="n"/>
-      <c r="C55" s="33" t="n"/>
-      <c r="D55" s="32" t="n"/>
-      <c r="E55" s="34" t="n"/>
-      <c r="F55" s="33" t="n"/>
-      <c r="G55" s="34" t="n"/>
-      <c r="H55" s="33" t="n"/>
-      <c r="I55" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L55" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M55" s="29">
+      <c r="B55" s="38" t="n"/>
+      <c r="D55" s="38" t="n"/>
+      <c r="I55" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J55" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K55" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L55" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M55" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="32" t="n"/>
-      <c r="C56" s="33" t="n"/>
-      <c r="D56" s="32" t="n"/>
-      <c r="E56" s="34" t="n"/>
-      <c r="F56" s="33" t="n"/>
-      <c r="G56" s="34" t="n"/>
-      <c r="H56" s="33" t="n"/>
-      <c r="I56" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L56" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M56" s="29">
+      <c r="B56" s="38" t="n"/>
+      <c r="D56" s="38" t="n"/>
+      <c r="I56" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J56" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K56" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L56" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M56" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="32" t="n"/>
-      <c r="C57" s="33" t="n"/>
-      <c r="D57" s="32" t="n"/>
-      <c r="E57" s="34" t="n"/>
-      <c r="F57" s="33" t="n"/>
-      <c r="G57" s="34" t="n"/>
-      <c r="H57" s="33" t="n"/>
-      <c r="I57" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L57" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M57" s="29">
+      <c r="B57" s="38" t="n"/>
+      <c r="D57" s="38" t="n"/>
+      <c r="I57" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J57" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K57" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L57" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M57" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="32" t="n"/>
-      <c r="C58" s="33" t="n"/>
-      <c r="D58" s="32" t="n"/>
-      <c r="E58" s="34" t="n"/>
-      <c r="F58" s="33" t="n"/>
-      <c r="G58" s="34" t="n"/>
-      <c r="H58" s="33" t="n"/>
-      <c r="I58" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L58" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M58" s="29">
+      <c r="B58" s="38" t="n"/>
+      <c r="D58" s="38" t="n"/>
+      <c r="I58" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J58" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K58" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L58" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M58" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="32" t="n"/>
-      <c r="C59" s="33" t="n"/>
-      <c r="D59" s="32" t="n"/>
-      <c r="E59" s="34" t="n"/>
-      <c r="F59" s="33" t="n"/>
-      <c r="G59" s="34" t="n"/>
-      <c r="H59" s="33" t="n"/>
-      <c r="I59" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L59" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M59" s="29">
+      <c r="B59" s="38" t="n"/>
+      <c r="D59" s="38" t="n"/>
+      <c r="I59" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J59" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K59" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L59" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M59" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="32" t="n"/>
-      <c r="C60" s="33" t="n"/>
-      <c r="D60" s="32" t="n"/>
-      <c r="E60" s="34" t="n"/>
-      <c r="F60" s="33" t="n"/>
-      <c r="G60" s="34" t="n"/>
-      <c r="H60" s="33" t="n"/>
-      <c r="I60" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L60" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M60" s="29">
+      <c r="B60" s="38" t="n"/>
+      <c r="D60" s="38" t="n"/>
+      <c r="I60" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J60" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K60" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L60" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M60" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="32" t="n"/>
-      <c r="C61" s="33" t="n"/>
-      <c r="D61" s="32" t="n"/>
-      <c r="E61" s="34" t="n"/>
-      <c r="F61" s="33" t="n"/>
-      <c r="G61" s="34" t="n"/>
-      <c r="H61" s="33" t="n"/>
-      <c r="I61" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L61" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M61" s="29">
+      <c r="B61" s="38" t="n"/>
+      <c r="D61" s="38" t="n"/>
+      <c r="I61" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J61" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K61" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L61" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M61" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="32" t="n"/>
-      <c r="C62" s="33" t="n"/>
-      <c r="D62" s="32" t="n"/>
-      <c r="E62" s="34" t="n"/>
-      <c r="F62" s="33" t="n"/>
-      <c r="G62" s="34" t="n"/>
-      <c r="H62" s="33" t="n"/>
-      <c r="I62" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L62" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M62" s="29">
+      <c r="B62" s="38" t="n"/>
+      <c r="D62" s="38" t="n"/>
+      <c r="I62" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J62" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K62" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L62" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M62" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="32" t="n"/>
-      <c r="C63" s="33" t="n"/>
-      <c r="D63" s="32" t="n"/>
-      <c r="E63" s="34" t="n"/>
-      <c r="F63" s="33" t="n"/>
-      <c r="G63" s="34" t="n"/>
-      <c r="H63" s="33" t="n"/>
-      <c r="I63" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L63" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M63" s="29">
+      <c r="B63" s="38" t="n"/>
+      <c r="D63" s="38" t="n"/>
+      <c r="I63" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J63" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K63" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L63" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M63" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="32" t="n"/>
-      <c r="C64" s="33" t="n"/>
-      <c r="D64" s="32" t="n"/>
-      <c r="E64" s="34" t="n"/>
-      <c r="F64" s="33" t="n"/>
-      <c r="G64" s="34" t="n"/>
-      <c r="H64" s="33" t="n"/>
-      <c r="I64" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L64" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M64" s="29">
+      <c r="B64" s="38" t="n"/>
+      <c r="D64" s="38" t="n"/>
+      <c r="I64" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J64" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K64" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L64" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M64" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="32" t="n"/>
-      <c r="C65" s="33" t="n"/>
-      <c r="D65" s="32" t="n"/>
-      <c r="E65" s="34" t="n"/>
-      <c r="F65" s="33" t="n"/>
-      <c r="G65" s="34" t="n"/>
-      <c r="H65" s="33" t="n"/>
-      <c r="I65" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L65" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M65" s="29">
+      <c r="B65" s="38" t="n"/>
+      <c r="D65" s="38" t="n"/>
+      <c r="I65" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J65" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K65" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L65" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M65" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="32" t="n"/>
-      <c r="C66" s="33" t="n"/>
-      <c r="D66" s="32" t="n"/>
-      <c r="E66" s="34" t="n"/>
-      <c r="F66" s="33" t="n"/>
-      <c r="G66" s="34" t="n"/>
-      <c r="H66" s="33" t="n"/>
-      <c r="I66" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L66" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M66" s="29">
+      <c r="B66" s="38" t="n"/>
+      <c r="D66" s="38" t="n"/>
+      <c r="I66" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J66" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K66" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L66" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M66" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="32" t="n"/>
-      <c r="C67" s="33" t="n"/>
-      <c r="D67" s="32" t="n"/>
-      <c r="E67" s="34" t="n"/>
-      <c r="F67" s="33" t="n"/>
-      <c r="G67" s="34" t="n"/>
-      <c r="H67" s="33" t="n"/>
-      <c r="I67" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L67" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M67" s="29">
+      <c r="B67" s="38" t="n"/>
+      <c r="D67" s="38" t="n"/>
+      <c r="I67" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J67" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K67" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L67" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M67" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="32" t="n"/>
-      <c r="C68" s="33" t="n"/>
-      <c r="D68" s="32" t="n"/>
-      <c r="E68" s="34" t="n"/>
-      <c r="F68" s="33" t="n"/>
-      <c r="G68" s="34" t="n"/>
-      <c r="H68" s="33" t="n"/>
-      <c r="I68" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L68" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M68" s="29">
+      <c r="B68" s="38" t="n"/>
+      <c r="D68" s="38" t="n"/>
+      <c r="I68" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J68" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K68" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L68" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M68" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="32" t="n"/>
-      <c r="C69" s="33" t="n"/>
-      <c r="D69" s="32" t="n"/>
-      <c r="E69" s="34" t="n"/>
-      <c r="F69" s="33" t="n"/>
-      <c r="G69" s="34" t="n"/>
-      <c r="H69" s="33" t="n"/>
-      <c r="I69" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L69" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M69" s="29">
+      <c r="B69" s="38" t="n"/>
+      <c r="D69" s="38" t="n"/>
+      <c r="I69" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J69" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K69" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L69" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M69" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="32" t="n"/>
-      <c r="C70" s="33" t="n"/>
-      <c r="D70" s="32" t="n"/>
-      <c r="E70" s="34" t="n"/>
-      <c r="F70" s="33" t="n"/>
-      <c r="G70" s="34" t="n"/>
-      <c r="H70" s="33" t="n"/>
-      <c r="I70" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J70" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K70" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L70" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M70" s="29">
+      <c r="B70" s="38" t="n"/>
+      <c r="D70" s="38" t="n"/>
+      <c r="I70" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J70" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K70" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L70" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M70" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="32" t="n"/>
-      <c r="C71" s="33" t="n"/>
-      <c r="D71" s="32" t="n"/>
-      <c r="E71" s="34" t="n"/>
-      <c r="F71" s="33" t="n"/>
-      <c r="G71" s="34" t="n"/>
-      <c r="H71" s="33" t="n"/>
-      <c r="I71" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J71" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K71" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L71" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M71" s="29">
+      <c r="B71" s="38" t="n"/>
+      <c r="D71" s="38" t="n"/>
+      <c r="I71" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J71" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K71" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L71" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M71" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="32" t="n"/>
-      <c r="C72" s="33" t="n"/>
-      <c r="D72" s="32" t="n"/>
-      <c r="E72" s="34" t="n"/>
-      <c r="F72" s="33" t="n"/>
-      <c r="G72" s="34" t="n"/>
-      <c r="H72" s="33" t="n"/>
-      <c r="I72" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J72" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K72" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L72" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M72" s="29">
+      <c r="B72" s="38" t="n"/>
+      <c r="D72" s="38" t="n"/>
+      <c r="I72" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J72" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K72" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L72" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M72" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="32" t="n"/>
-      <c r="C73" s="33" t="n"/>
-      <c r="D73" s="32" t="n"/>
-      <c r="E73" s="34" t="n"/>
-      <c r="F73" s="33" t="n"/>
-      <c r="G73" s="34" t="n"/>
-      <c r="H73" s="33" t="n"/>
-      <c r="I73" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J73" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K73" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L73" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M73" s="29">
+      <c r="B73" s="38" t="n"/>
+      <c r="D73" s="38" t="n"/>
+      <c r="I73" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J73" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K73" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L73" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M73" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="32" t="n"/>
-      <c r="C74" s="33" t="n"/>
-      <c r="D74" s="32" t="n"/>
-      <c r="E74" s="34" t="n"/>
-      <c r="F74" s="33" t="n"/>
-      <c r="G74" s="34" t="n"/>
-      <c r="H74" s="33" t="n"/>
-      <c r="I74" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J74" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K74" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L74" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M74" s="29">
+      <c r="B74" s="38" t="n"/>
+      <c r="D74" s="38" t="n"/>
+      <c r="I74" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J74" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K74" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L74" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M74" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="32" t="n"/>
-      <c r="C75" s="33" t="n"/>
-      <c r="D75" s="32" t="n"/>
-      <c r="E75" s="34" t="n"/>
-      <c r="F75" s="33" t="n"/>
-      <c r="G75" s="34" t="n"/>
-      <c r="H75" s="33" t="n"/>
-      <c r="I75" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J75" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K75" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L75" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M75" s="29">
+      <c r="B75" s="38" t="n"/>
+      <c r="D75" s="38" t="n"/>
+      <c r="I75" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J75" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K75" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L75" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M75" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="32" t="n"/>
-      <c r="C76" s="33" t="n"/>
-      <c r="D76" s="32" t="n"/>
-      <c r="E76" s="34" t="n"/>
-      <c r="F76" s="33" t="n"/>
-      <c r="G76" s="34" t="n"/>
-      <c r="H76" s="33" t="n"/>
-      <c r="I76" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J76" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K76" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L76" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M76" s="29">
+      <c r="B76" s="38" t="n"/>
+      <c r="D76" s="38" t="n"/>
+      <c r="I76" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J76" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K76" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L76" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M76" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="32" t="n"/>
-      <c r="C77" s="33" t="n"/>
-      <c r="D77" s="32" t="n"/>
-      <c r="E77" s="34" t="n"/>
-      <c r="F77" s="33" t="n"/>
-      <c r="G77" s="34" t="n"/>
-      <c r="H77" s="33" t="n"/>
-      <c r="I77" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J77" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K77" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L77" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M77" s="29">
+      <c r="B77" s="38" t="n"/>
+      <c r="D77" s="38" t="n"/>
+      <c r="I77" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J77" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K77" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L77" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M77" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="32" t="n"/>
-      <c r="C78" s="33" t="n"/>
-      <c r="D78" s="32" t="n"/>
-      <c r="E78" s="34" t="n"/>
-      <c r="F78" s="33" t="n"/>
-      <c r="G78" s="34" t="n"/>
-      <c r="H78" s="33" t="n"/>
-      <c r="I78" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J78" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K78" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L78" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M78" s="29">
+      <c r="B78" s="38" t="n"/>
+      <c r="D78" s="38" t="n"/>
+      <c r="I78" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J78" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K78" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L78" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M78" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="32" t="n"/>
-      <c r="C79" s="33" t="n"/>
-      <c r="D79" s="32" t="n"/>
-      <c r="E79" s="34" t="n"/>
-      <c r="F79" s="33" t="n"/>
-      <c r="G79" s="34" t="n"/>
-      <c r="H79" s="33" t="n"/>
-      <c r="I79" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J79" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K79" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L79" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M79" s="29">
+      <c r="B79" s="38" t="n"/>
+      <c r="D79" s="38" t="n"/>
+      <c r="I79" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J79" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K79" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L79" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M79" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="32" t="n"/>
-      <c r="C80" s="33" t="n"/>
-      <c r="D80" s="32" t="n"/>
-      <c r="E80" s="34" t="n"/>
-      <c r="F80" s="33" t="n"/>
-      <c r="G80" s="34" t="n"/>
-      <c r="H80" s="33" t="n"/>
-      <c r="I80" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J80" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K80" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L80" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M80" s="29">
+      <c r="B80" s="38" t="n"/>
+      <c r="D80" s="38" t="n"/>
+      <c r="I80" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J80" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K80" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L80" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M80" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="32" t="n"/>
-      <c r="C81" s="33" t="n"/>
-      <c r="D81" s="32" t="n"/>
-      <c r="E81" s="34" t="n"/>
-      <c r="F81" s="33" t="n"/>
-      <c r="G81" s="34" t="n"/>
-      <c r="H81" s="33" t="n"/>
-      <c r="I81" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J81" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K81" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L81" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M81" s="29">
+      <c r="B81" s="38" t="n"/>
+      <c r="D81" s="38" t="n"/>
+      <c r="I81" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J81" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K81" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L81" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M81" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="32" t="n"/>
-      <c r="C82" s="33" t="n"/>
-      <c r="D82" s="32" t="n"/>
-      <c r="E82" s="34" t="n"/>
-      <c r="F82" s="33" t="n"/>
-      <c r="G82" s="34" t="n"/>
-      <c r="H82" s="33" t="n"/>
-      <c r="I82" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J82" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K82" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L82" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M82" s="29">
+      <c r="B82" s="38" t="n"/>
+      <c r="D82" s="38" t="n"/>
+      <c r="I82" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J82" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K82" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L82" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M82" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="32" t="n"/>
-      <c r="C83" s="33" t="n"/>
-      <c r="D83" s="32" t="n"/>
-      <c r="E83" s="34" t="n"/>
-      <c r="F83" s="33" t="n"/>
-      <c r="G83" s="34" t="n"/>
-      <c r="H83" s="33" t="n"/>
-      <c r="I83" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J83" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K83" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L83" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M83" s="29">
+      <c r="B83" s="38" t="n"/>
+      <c r="D83" s="38" t="n"/>
+      <c r="I83" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J83" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K83" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L83" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M83" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="32" t="n"/>
-      <c r="C84" s="33" t="n"/>
-      <c r="D84" s="32" t="n"/>
-      <c r="E84" s="34" t="n"/>
-      <c r="F84" s="33" t="n"/>
-      <c r="G84" s="34" t="n"/>
-      <c r="H84" s="33" t="n"/>
-      <c r="I84" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J84" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K84" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L84" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M84" s="29">
+      <c r="B84" s="38" t="n"/>
+      <c r="D84" s="38" t="n"/>
+      <c r="I84" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J84" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K84" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L84" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M84" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="32" t="n"/>
-      <c r="C85" s="33" t="n"/>
-      <c r="D85" s="32" t="n"/>
-      <c r="E85" s="34" t="n"/>
-      <c r="F85" s="33" t="n"/>
-      <c r="G85" s="34" t="n"/>
-      <c r="H85" s="33" t="n"/>
-      <c r="I85" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J85" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K85" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L85" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M85" s="29">
+      <c r="B85" s="38" t="n"/>
+      <c r="D85" s="38" t="n"/>
+      <c r="I85" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J85" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K85" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L85" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M85" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="32" t="n"/>
-      <c r="C86" s="33" t="n"/>
-      <c r="D86" s="32" t="n"/>
-      <c r="E86" s="34" t="n"/>
-      <c r="F86" s="33" t="n"/>
-      <c r="G86" s="34" t="n"/>
-      <c r="H86" s="33" t="n"/>
-      <c r="I86" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J86" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K86" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L86" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M86" s="29">
+      <c r="B86" s="38" t="n"/>
+      <c r="D86" s="38" t="n"/>
+      <c r="I86" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J86" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K86" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L86" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M86" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="32" t="n"/>
-      <c r="C87" s="33" t="n"/>
-      <c r="D87" s="32" t="n"/>
-      <c r="E87" s="34" t="n"/>
-      <c r="F87" s="33" t="n"/>
-      <c r="G87" s="34" t="n"/>
-      <c r="H87" s="33" t="n"/>
-      <c r="I87" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J87" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K87" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L87" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M87" s="29">
+      <c r="B87" s="38" t="n"/>
+      <c r="D87" s="38" t="n"/>
+      <c r="I87" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J87" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K87" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L87" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M87" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="32" t="n"/>
-      <c r="C88" s="33" t="n"/>
-      <c r="D88" s="32" t="n"/>
-      <c r="E88" s="34" t="n"/>
-      <c r="F88" s="33" t="n"/>
-      <c r="G88" s="34" t="n"/>
-      <c r="H88" s="33" t="n"/>
-      <c r="I88" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J88" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K88" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L88" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M88" s="29">
+      <c r="B88" s="38" t="n"/>
+      <c r="D88" s="38" t="n"/>
+      <c r="I88" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J88" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K88" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L88" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M88" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="32" t="n"/>
-      <c r="C89" s="33" t="n"/>
-      <c r="D89" s="32" t="n"/>
-      <c r="E89" s="34" t="n"/>
-      <c r="F89" s="33" t="n"/>
-      <c r="G89" s="34" t="n"/>
-      <c r="H89" s="33" t="n"/>
-      <c r="I89" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J89" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K89" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L89" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M89" s="29">
+      <c r="B89" s="38" t="n"/>
+      <c r="D89" s="38" t="n"/>
+      <c r="I89" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J89" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K89" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L89" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M89" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="32" t="n"/>
-      <c r="C90" s="33" t="n"/>
-      <c r="D90" s="32" t="n"/>
-      <c r="E90" s="34" t="n"/>
-      <c r="F90" s="33" t="n"/>
-      <c r="G90" s="34" t="n"/>
-      <c r="H90" s="33" t="n"/>
-      <c r="I90" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J90" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K90" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L90" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M90" s="29">
+      <c r="B90" s="38" t="n"/>
+      <c r="D90" s="38" t="n"/>
+      <c r="I90" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J90" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K90" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L90" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M90" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="32" t="n"/>
-      <c r="C91" s="33" t="n"/>
-      <c r="D91" s="32" t="n"/>
-      <c r="E91" s="34" t="n"/>
-      <c r="F91" s="33" t="n"/>
-      <c r="G91" s="34" t="n"/>
-      <c r="H91" s="33" t="n"/>
-      <c r="I91" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J91" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K91" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L91" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M91" s="29">
+      <c r="B91" s="38" t="n"/>
+      <c r="D91" s="38" t="n"/>
+      <c r="I91" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J91" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K91" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L91" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M91" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="32" t="n"/>
-      <c r="C92" s="33" t="n"/>
-      <c r="D92" s="32" t="n"/>
-      <c r="E92" s="34" t="n"/>
-      <c r="F92" s="33" t="n"/>
-      <c r="G92" s="34" t="n"/>
-      <c r="H92" s="33" t="n"/>
-      <c r="I92" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J92" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K92" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L92" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M92" s="29">
+      <c r="B92" s="38" t="n"/>
+      <c r="D92" s="38" t="n"/>
+      <c r="I92" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J92" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K92" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L92" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M92" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="32" t="n"/>
-      <c r="C93" s="33" t="n"/>
-      <c r="D93" s="32" t="n"/>
-      <c r="E93" s="34" t="n"/>
-      <c r="F93" s="33" t="n"/>
-      <c r="G93" s="34" t="n"/>
-      <c r="H93" s="33" t="n"/>
-      <c r="I93" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J93" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K93" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L93" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M93" s="29">
+      <c r="B93" s="38" t="n"/>
+      <c r="D93" s="38" t="n"/>
+      <c r="I93" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J93" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K93" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L93" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M93" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="32" t="n"/>
-      <c r="C94" s="33" t="n"/>
-      <c r="D94" s="32" t="n"/>
-      <c r="E94" s="34" t="n"/>
-      <c r="F94" s="33" t="n"/>
-      <c r="G94" s="34" t="n"/>
-      <c r="H94" s="33" t="n"/>
-      <c r="I94" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J94" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K94" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L94" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M94" s="29">
+      <c r="B94" s="38" t="n"/>
+      <c r="D94" s="38" t="n"/>
+      <c r="I94" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J94" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K94" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L94" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M94" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="32" t="n"/>
-      <c r="C95" s="33" t="n"/>
-      <c r="D95" s="32" t="n"/>
-      <c r="E95" s="34" t="n"/>
-      <c r="F95" s="33" t="n"/>
-      <c r="G95" s="34" t="n"/>
-      <c r="H95" s="33" t="n"/>
-      <c r="I95" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J95" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K95" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L95" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M95" s="29">
+      <c r="B95" s="38" t="n"/>
+      <c r="D95" s="38" t="n"/>
+      <c r="I95" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J95" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K95" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L95" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M95" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="32" t="n"/>
-      <c r="C96" s="33" t="n"/>
-      <c r="D96" s="32" t="n"/>
-      <c r="E96" s="34" t="n"/>
-      <c r="F96" s="33" t="n"/>
-      <c r="G96" s="34" t="n"/>
-      <c r="H96" s="33" t="n"/>
-      <c r="I96" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J96" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K96" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L96" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M96" s="29">
+      <c r="B96" s="38" t="n"/>
+      <c r="D96" s="38" t="n"/>
+      <c r="I96" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J96" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K96" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L96" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M96" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="32" t="n"/>
-      <c r="C97" s="33" t="n"/>
-      <c r="D97" s="32" t="n"/>
-      <c r="E97" s="34" t="n"/>
-      <c r="F97" s="33" t="n"/>
-      <c r="G97" s="34" t="n"/>
-      <c r="H97" s="33" t="n"/>
-      <c r="I97" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J97" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K97" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L97" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M97" s="29">
+      <c r="B97" s="38" t="n"/>
+      <c r="D97" s="38" t="n"/>
+      <c r="I97" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J97" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K97" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L97" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M97" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="32" t="n"/>
-      <c r="C98" s="33" t="n"/>
-      <c r="D98" s="32" t="n"/>
-      <c r="E98" s="34" t="n"/>
-      <c r="F98" s="33" t="n"/>
-      <c r="G98" s="34" t="n"/>
-      <c r="H98" s="33" t="n"/>
-      <c r="I98" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J98" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K98" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L98" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M98" s="29">
+      <c r="B98" s="38" t="n"/>
+      <c r="D98" s="38" t="n"/>
+      <c r="I98" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J98" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K98" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L98" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M98" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="32" t="n"/>
-      <c r="C99" s="33" t="n"/>
-      <c r="D99" s="32" t="n"/>
-      <c r="E99" s="34" t="n"/>
-      <c r="F99" s="33" t="n"/>
-      <c r="G99" s="34" t="n"/>
-      <c r="H99" s="33" t="n"/>
-      <c r="I99" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J99" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K99" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L99" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M99" s="29">
+      <c r="B99" s="38" t="n"/>
+      <c r="D99" s="38" t="n"/>
+      <c r="I99" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J99" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K99" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L99" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M99" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="32" t="n"/>
-      <c r="C100" s="33" t="n"/>
-      <c r="D100" s="32" t="n"/>
-      <c r="E100" s="34" t="n"/>
-      <c r="F100" s="33" t="n"/>
-      <c r="G100" s="34" t="n"/>
-      <c r="H100" s="33" t="n"/>
-      <c r="I100" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J100" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K100" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L100" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M100" s="29">
+      <c r="B100" s="38" t="n"/>
+      <c r="D100" s="38" t="n"/>
+      <c r="I100" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J100" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K100" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L100" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M100" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="32" t="n"/>
-      <c r="C101" s="33" t="n"/>
-      <c r="D101" s="32" t="n"/>
-      <c r="E101" s="34" t="n"/>
-      <c r="F101" s="33" t="n"/>
-      <c r="G101" s="34" t="n"/>
-      <c r="H101" s="33" t="n"/>
-      <c r="I101" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J101" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K101" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L101" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M101" s="29">
+      <c r="B101" s="38" t="n"/>
+      <c r="D101" s="38" t="n"/>
+      <c r="I101" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J101" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K101" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L101" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M101" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="32" t="n"/>
-      <c r="C102" s="33" t="n"/>
-      <c r="D102" s="32" t="n"/>
-      <c r="E102" s="34" t="n"/>
-      <c r="F102" s="33" t="n"/>
-      <c r="G102" s="34" t="n"/>
-      <c r="H102" s="33" t="n"/>
-      <c r="I102" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J102" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K102" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L102" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M102" s="29">
+      <c r="B102" s="38" t="n"/>
+      <c r="D102" s="38" t="n"/>
+      <c r="I102" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J102" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K102" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L102" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M102" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="32" t="n"/>
-      <c r="C103" s="33" t="n"/>
-      <c r="D103" s="32" t="n"/>
-      <c r="E103" s="34" t="n"/>
-      <c r="F103" s="33" t="n"/>
-      <c r="G103" s="34" t="n"/>
-      <c r="H103" s="33" t="n"/>
-      <c r="I103" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J103" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K103" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L103" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M103" s="29">
+      <c r="B103" s="38" t="n"/>
+      <c r="D103" s="38" t="n"/>
+      <c r="I103" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J103" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K103" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L103" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M103" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="32" t="n"/>
-      <c r="C104" s="33" t="n"/>
-      <c r="D104" s="32" t="n"/>
-      <c r="E104" s="34" t="n"/>
-      <c r="F104" s="33" t="n"/>
-      <c r="G104" s="34" t="n"/>
-      <c r="H104" s="33" t="n"/>
-      <c r="I104" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J104" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K104" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L104" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M104" s="29">
+      <c r="B104" s="38" t="n"/>
+      <c r="D104" s="38" t="n"/>
+      <c r="I104" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J104" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K104" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L104" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M104" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="32" t="n"/>
-      <c r="C105" s="33" t="n"/>
-      <c r="D105" s="32" t="n"/>
-      <c r="E105" s="34" t="n"/>
-      <c r="F105" s="33" t="n"/>
-      <c r="G105" s="34" t="n"/>
-      <c r="H105" s="33" t="n"/>
-      <c r="I105" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J105" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K105" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L105" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M105" s="29">
+      <c r="B105" s="38" t="n"/>
+      <c r="D105" s="38" t="n"/>
+      <c r="I105" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J105" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K105" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L105" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M105" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="32" t="n"/>
-      <c r="C106" s="33" t="n"/>
-      <c r="D106" s="32" t="n"/>
-      <c r="E106" s="34" t="n"/>
-      <c r="F106" s="33" t="n"/>
-      <c r="G106" s="34" t="n"/>
-      <c r="H106" s="33" t="n"/>
-      <c r="I106" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J106" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K106" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L106" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M106" s="29">
+      <c r="B106" s="38" t="n"/>
+      <c r="D106" s="38" t="n"/>
+      <c r="I106" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J106" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K106" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L106" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M106" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="32" t="n"/>
-      <c r="C107" s="33" t="n"/>
-      <c r="D107" s="32" t="n"/>
-      <c r="E107" s="34" t="n"/>
-      <c r="F107" s="33" t="n"/>
-      <c r="G107" s="34" t="n"/>
-      <c r="H107" s="33" t="n"/>
-      <c r="I107" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J107" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K107" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L107" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M107" s="29">
+      <c r="B107" s="38" t="n"/>
+      <c r="D107" s="38" t="n"/>
+      <c r="I107" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J107" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K107" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L107" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M107" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="32" t="n"/>
-      <c r="C108" s="33" t="n"/>
-      <c r="D108" s="32" t="n"/>
-      <c r="E108" s="34" t="n"/>
-      <c r="F108" s="33" t="n"/>
-      <c r="G108" s="34" t="n"/>
-      <c r="H108" s="33" t="n"/>
-      <c r="I108" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J108" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K108" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L108" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M108" s="29">
+      <c r="B108" s="38" t="n"/>
+      <c r="D108" s="38" t="n"/>
+      <c r="I108" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J108" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K108" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L108" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M108" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="32" t="n"/>
-      <c r="C109" s="33" t="n"/>
-      <c r="D109" s="32" t="n"/>
-      <c r="E109" s="34" t="n"/>
-      <c r="F109" s="33" t="n"/>
-      <c r="G109" s="34" t="n"/>
-      <c r="H109" s="33" t="n"/>
-      <c r="I109" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J109" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K109" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L109" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M109" s="29">
+      <c r="B109" s="38" t="n"/>
+      <c r="D109" s="38" t="n"/>
+      <c r="I109" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J109" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K109" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L109" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M109" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="32" t="n"/>
-      <c r="C110" s="33" t="n"/>
-      <c r="D110" s="32" t="n"/>
-      <c r="E110" s="34" t="n"/>
-      <c r="F110" s="33" t="n"/>
-      <c r="G110" s="34" t="n"/>
-      <c r="H110" s="33" t="n"/>
-      <c r="I110" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J110" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K110" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L110" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M110" s="29">
+      <c r="B110" s="38" t="n"/>
+      <c r="D110" s="38" t="n"/>
+      <c r="I110" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J110" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K110" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L110" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M110" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="32" t="n"/>
-      <c r="C111" s="33" t="n"/>
-      <c r="D111" s="32" t="n"/>
-      <c r="E111" s="34" t="n"/>
-      <c r="F111" s="33" t="n"/>
-      <c r="G111" s="34" t="n"/>
-      <c r="H111" s="33" t="n"/>
-      <c r="I111" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J111" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K111" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L111" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M111" s="29">
+      <c r="B111" s="38" t="n"/>
+      <c r="D111" s="38" t="n"/>
+      <c r="I111" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J111" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K111" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L111" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M111" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="32" t="n"/>
-      <c r="C112" s="33" t="n"/>
-      <c r="D112" s="32" t="n"/>
-      <c r="E112" s="34" t="n"/>
-      <c r="F112" s="33" t="n"/>
-      <c r="G112" s="34" t="n"/>
-      <c r="H112" s="33" t="n"/>
-      <c r="I112" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J112" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K112" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L112" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M112" s="29">
+      <c r="B112" s="38" t="n"/>
+      <c r="D112" s="38" t="n"/>
+      <c r="I112" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J112" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K112" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L112" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M112" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="32" t="n"/>
-      <c r="C113" s="33" t="n"/>
-      <c r="D113" s="32" t="n"/>
-      <c r="E113" s="34" t="n"/>
-      <c r="F113" s="33" t="n"/>
-      <c r="G113" s="34" t="n"/>
-      <c r="H113" s="33" t="n"/>
-      <c r="I113" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J113" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K113" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L113" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M113" s="29">
+      <c r="B113" s="38" t="n"/>
+      <c r="D113" s="38" t="n"/>
+      <c r="I113" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J113" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K113" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L113" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M113" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="32" t="n"/>
-      <c r="C114" s="33" t="n"/>
-      <c r="D114" s="32" t="n"/>
-      <c r="E114" s="34" t="n"/>
-      <c r="F114" s="33" t="n"/>
-      <c r="G114" s="34" t="n"/>
-      <c r="H114" s="33" t="n"/>
-      <c r="I114" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J114" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K114" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L114" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M114" s="29">
+      <c r="B114" s="38" t="n"/>
+      <c r="D114" s="38" t="n"/>
+      <c r="I114" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J114" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K114" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L114" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M114" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="32" t="n"/>
-      <c r="C115" s="33" t="n"/>
-      <c r="D115" s="32" t="n"/>
-      <c r="E115" s="34" t="n"/>
-      <c r="F115" s="33" t="n"/>
-      <c r="G115" s="34" t="n"/>
-      <c r="H115" s="33" t="n"/>
-      <c r="I115" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J115" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K115" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L115" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M115" s="29">
+      <c r="B115" s="38" t="n"/>
+      <c r="D115" s="38" t="n"/>
+      <c r="I115" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J115" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K115" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L115" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M115" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="B116" s="32" t="n"/>
-      <c r="C116" s="33" t="n"/>
-      <c r="D116" s="32" t="n"/>
-      <c r="E116" s="34" t="n"/>
-      <c r="F116" s="33" t="n"/>
-      <c r="G116" s="34" t="n"/>
-      <c r="H116" s="33" t="n"/>
-      <c r="I116" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J116" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K116" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L116" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M116" s="29">
+      <c r="B116" s="38" t="n"/>
+      <c r="D116" s="38" t="n"/>
+      <c r="I116" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J116" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K116" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L116" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M116" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="32" t="n"/>
-      <c r="C117" s="33" t="n"/>
-      <c r="D117" s="32" t="n"/>
-      <c r="E117" s="34" t="n"/>
-      <c r="F117" s="33" t="n"/>
-      <c r="G117" s="34" t="n"/>
-      <c r="H117" s="33" t="n"/>
-      <c r="I117" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J117" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K117" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L117" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M117" s="29">
+      <c r="B117" s="38" t="n"/>
+      <c r="D117" s="38" t="n"/>
+      <c r="I117" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J117" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K117" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L117" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M117" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="B118" s="32" t="n"/>
-      <c r="C118" s="33" t="n"/>
-      <c r="D118" s="32" t="n"/>
-      <c r="E118" s="34" t="n"/>
-      <c r="F118" s="33" t="n"/>
-      <c r="G118" s="34" t="n"/>
-      <c r="H118" s="33" t="n"/>
-      <c r="I118" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J118" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K118" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L118" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M118" s="29">
+      <c r="B118" s="38" t="n"/>
+      <c r="D118" s="38" t="n"/>
+      <c r="I118" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J118" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K118" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L118" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M118" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="32" t="n"/>
-      <c r="C119" s="33" t="n"/>
-      <c r="D119" s="32" t="n"/>
-      <c r="E119" s="34" t="n"/>
-      <c r="F119" s="33" t="n"/>
-      <c r="G119" s="34" t="n"/>
-      <c r="H119" s="33" t="n"/>
-      <c r="I119" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J119" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K119" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L119" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M119" s="29">
+      <c r="B119" s="38" t="n"/>
+      <c r="D119" s="38" t="n"/>
+      <c r="I119" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J119" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K119" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L119" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M119" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="B120" s="32" t="n"/>
-      <c r="C120" s="33" t="n"/>
-      <c r="D120" s="32" t="n"/>
-      <c r="E120" s="34" t="n"/>
-      <c r="F120" s="33" t="n"/>
-      <c r="G120" s="34" t="n"/>
-      <c r="H120" s="33" t="n"/>
-      <c r="I120" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J120" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K120" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L120" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M120" s="29">
+      <c r="B120" s="38" t="n"/>
+      <c r="D120" s="38" t="n"/>
+      <c r="I120" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J120" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K120" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L120" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M120" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="B121" s="32" t="n"/>
-      <c r="C121" s="33" t="n"/>
-      <c r="D121" s="32" t="n"/>
-      <c r="E121" s="34" t="n"/>
-      <c r="F121" s="33" t="n"/>
-      <c r="G121" s="34" t="n"/>
-      <c r="H121" s="33" t="n"/>
-      <c r="I121" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J121" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K121" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L121" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M121" s="29">
+      <c r="B121" s="38" t="n"/>
+      <c r="D121" s="38" t="n"/>
+      <c r="I121" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J121" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K121" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L121" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M121" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="32" t="n"/>
-      <c r="C122" s="33" t="n"/>
-      <c r="D122" s="32" t="n"/>
-      <c r="E122" s="34" t="n"/>
-      <c r="F122" s="33" t="n"/>
-      <c r="G122" s="34" t="n"/>
-      <c r="H122" s="33" t="n"/>
-      <c r="I122" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J122" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K122" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L122" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M122" s="29">
+      <c r="B122" s="38" t="n"/>
+      <c r="D122" s="38" t="n"/>
+      <c r="I122" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J122" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K122" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L122" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M122" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="32" t="n"/>
-      <c r="C123" s="33" t="n"/>
-      <c r="D123" s="32" t="n"/>
-      <c r="E123" s="34" t="n"/>
-      <c r="F123" s="33" t="n"/>
-      <c r="G123" s="34" t="n"/>
-      <c r="H123" s="33" t="n"/>
-      <c r="I123" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J123" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K123" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L123" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M123" s="29">
+      <c r="B123" s="38" t="n"/>
+      <c r="D123" s="38" t="n"/>
+      <c r="I123" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J123" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K123" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L123" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M123" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="32" t="n"/>
-      <c r="C124" s="33" t="n"/>
-      <c r="D124" s="32" t="n"/>
-      <c r="E124" s="34" t="n"/>
-      <c r="F124" s="33" t="n"/>
-      <c r="G124" s="34" t="n"/>
-      <c r="H124" s="33" t="n"/>
-      <c r="I124" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J124" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K124" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L124" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M124" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="32" t="n"/>
-      <c r="C125" s="33" t="n"/>
-      <c r="D125" s="32" t="n"/>
-      <c r="E125" s="34" t="n"/>
-      <c r="F125" s="33" t="n"/>
-      <c r="G125" s="34" t="n"/>
-      <c r="H125" s="33" t="n"/>
-      <c r="I125" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J125" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K125" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L125" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M125" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="32" t="n"/>
-      <c r="C126" s="33" t="n"/>
-      <c r="D126" s="32" t="n"/>
-      <c r="E126" s="34" t="n"/>
-      <c r="F126" s="33" t="n"/>
-      <c r="G126" s="34" t="n"/>
-      <c r="H126" s="33" t="n"/>
-      <c r="I126" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J126" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K126" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L126" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M126" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="32" t="n"/>
-      <c r="C127" s="33" t="n"/>
-      <c r="D127" s="32" t="n"/>
-      <c r="E127" s="34" t="n"/>
-      <c r="F127" s="33" t="n"/>
-      <c r="G127" s="34" t="n"/>
-      <c r="H127" s="33" t="n"/>
-      <c r="I127" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J127" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K127" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L127" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M127" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="32" t="n"/>
-      <c r="C128" s="33" t="n"/>
-      <c r="D128" s="32" t="n"/>
-      <c r="E128" s="34" t="n"/>
-      <c r="F128" s="33" t="n"/>
-      <c r="G128" s="34" t="n"/>
-      <c r="H128" s="33" t="n"/>
-      <c r="I128" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J128" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K128" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L128" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M128" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" s="32" t="n"/>
-      <c r="C129" s="33" t="n"/>
-      <c r="D129" s="32" t="n"/>
-      <c r="E129" s="34" t="n"/>
-      <c r="F129" s="33" t="n"/>
-      <c r="G129" s="34" t="n"/>
-      <c r="H129" s="33" t="n"/>
-      <c r="I129" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J129" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K129" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L129" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M129" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="32" t="n"/>
-      <c r="C130" s="33" t="n"/>
-      <c r="D130" s="32" t="n"/>
-      <c r="E130" s="34" t="n"/>
-      <c r="F130" s="33" t="n"/>
-      <c r="G130" s="34" t="n"/>
-      <c r="H130" s="33" t="n"/>
-      <c r="I130" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J130" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K130" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L130" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M130" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="32" t="n"/>
-      <c r="C131" s="33" t="n"/>
-      <c r="D131" s="32" t="n"/>
-      <c r="E131" s="34" t="n"/>
-      <c r="F131" s="33" t="n"/>
-      <c r="G131" s="34" t="n"/>
-      <c r="H131" s="33" t="n"/>
-      <c r="I131" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J131" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K131" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L131" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M131" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="32" t="n"/>
-      <c r="C132" s="33" t="n"/>
-      <c r="D132" s="32" t="n"/>
-      <c r="E132" s="34" t="n"/>
-      <c r="F132" s="33" t="n"/>
-      <c r="G132" s="34" t="n"/>
-      <c r="H132" s="33" t="n"/>
-      <c r="I132" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J132" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K132" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L132" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M132" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="32" t="n"/>
-      <c r="C133" s="33" t="n"/>
-      <c r="D133" s="32" t="n"/>
-      <c r="E133" s="34" t="n"/>
-      <c r="F133" s="33" t="n"/>
-      <c r="G133" s="34" t="n"/>
-      <c r="H133" s="33" t="n"/>
-      <c r="I133" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J133" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K133" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L133" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M133" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="32" t="n"/>
-      <c r="C134" s="33" t="n"/>
-      <c r="D134" s="32" t="n"/>
-      <c r="E134" s="34" t="n"/>
-      <c r="F134" s="33" t="n"/>
-      <c r="G134" s="34" t="n"/>
-      <c r="H134" s="33" t="n"/>
-      <c r="I134" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J134" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K134" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L134" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M134" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="32" t="n"/>
-      <c r="C135" s="33" t="n"/>
-      <c r="D135" s="32" t="n"/>
-      <c r="E135" s="34" t="n"/>
-      <c r="F135" s="33" t="n"/>
-      <c r="G135" s="34" t="n"/>
-      <c r="H135" s="33" t="n"/>
-      <c r="I135" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J135" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K135" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L135" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M135" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="B136" s="32" t="n"/>
-      <c r="C136" s="33" t="n"/>
-      <c r="D136" s="32" t="n"/>
-      <c r="E136" s="34" t="n"/>
-      <c r="F136" s="33" t="n"/>
-      <c r="G136" s="34" t="n"/>
-      <c r="H136" s="33" t="n"/>
-      <c r="I136" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J136" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K136" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L136" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M136" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="32" t="n"/>
-      <c r="C137" s="33" t="n"/>
-      <c r="D137" s="32" t="n"/>
-      <c r="E137" s="34" t="n"/>
-      <c r="F137" s="33" t="n"/>
-      <c r="G137" s="34" t="n"/>
-      <c r="H137" s="33" t="n"/>
-      <c r="I137" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J137" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K137" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L137" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M137" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" s="32" t="n"/>
-      <c r="C138" s="33" t="n"/>
-      <c r="D138" s="32" t="n"/>
-      <c r="E138" s="34" t="n"/>
-      <c r="F138" s="33" t="n"/>
-      <c r="G138" s="34" t="n"/>
-      <c r="H138" s="33" t="n"/>
-      <c r="I138" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J138" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K138" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L138" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M138" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="32" t="n"/>
-      <c r="C139" s="33" t="n"/>
-      <c r="D139" s="32" t="n"/>
-      <c r="E139" s="34" t="n"/>
-      <c r="F139" s="33" t="n"/>
-      <c r="G139" s="34" t="n"/>
-      <c r="H139" s="33" t="n"/>
-      <c r="I139" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J139" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K139" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L139" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M139" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="B140" s="32" t="n"/>
-      <c r="C140" s="33" t="n"/>
-      <c r="D140" s="32" t="n"/>
-      <c r="E140" s="34" t="n"/>
-      <c r="F140" s="33" t="n"/>
-      <c r="G140" s="34" t="n"/>
-      <c r="H140" s="33" t="n"/>
-      <c r="I140" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J140" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K140" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L140" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M140" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="B141" s="32" t="n"/>
-      <c r="C141" s="33" t="n"/>
-      <c r="D141" s="32" t="n"/>
-      <c r="E141" s="34" t="n"/>
-      <c r="F141" s="33" t="n"/>
-      <c r="G141" s="34" t="n"/>
-      <c r="H141" s="33" t="n"/>
-      <c r="I141" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J141" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K141" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L141" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M141" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="32" t="n"/>
-      <c r="C142" s="33" t="n"/>
-      <c r="D142" s="32" t="n"/>
-      <c r="E142" s="34" t="n"/>
-      <c r="F142" s="33" t="n"/>
-      <c r="G142" s="34" t="n"/>
-      <c r="H142" s="33" t="n"/>
-      <c r="I142" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J142" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K142" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L142" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M142" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="32" t="n"/>
-      <c r="C143" s="33" t="n"/>
-      <c r="D143" s="32" t="n"/>
-      <c r="E143" s="34" t="n"/>
-      <c r="F143" s="33" t="n"/>
-      <c r="G143" s="34" t="n"/>
-      <c r="H143" s="33" t="n"/>
-      <c r="I143" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J143" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K143" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L143" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M143" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="32" t="n"/>
-      <c r="C144" s="33" t="n"/>
-      <c r="D144" s="32" t="n"/>
-      <c r="E144" s="34" t="n"/>
-      <c r="F144" s="33" t="n"/>
-      <c r="G144" s="34" t="n"/>
-      <c r="H144" s="33" t="n"/>
-      <c r="I144" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J144" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K144" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L144" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M144" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="32" t="n"/>
-      <c r="C145" s="33" t="n"/>
-      <c r="D145" s="32" t="n"/>
-      <c r="E145" s="34" t="n"/>
-      <c r="F145" s="33" t="n"/>
-      <c r="G145" s="34" t="n"/>
-      <c r="H145" s="33" t="n"/>
-      <c r="I145" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J145" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K145" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L145" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M145" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="32" t="n"/>
-      <c r="C146" s="33" t="n"/>
-      <c r="D146" s="32" t="n"/>
-      <c r="E146" s="34" t="n"/>
-      <c r="F146" s="33" t="n"/>
-      <c r="G146" s="34" t="n"/>
-      <c r="H146" s="33" t="n"/>
-      <c r="I146" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J146" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K146" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L146" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M146" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="B147" s="32" t="n"/>
-      <c r="C147" s="33" t="n"/>
-      <c r="D147" s="32" t="n"/>
-      <c r="E147" s="34" t="n"/>
-      <c r="F147" s="33" t="n"/>
-      <c r="G147" s="34" t="n"/>
-      <c r="H147" s="33" t="n"/>
-      <c r="I147" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J147" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K147" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L147" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M147" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="B148" s="32" t="n"/>
-      <c r="C148" s="33" t="n"/>
-      <c r="D148" s="32" t="n"/>
-      <c r="E148" s="34" t="n"/>
-      <c r="F148" s="33" t="n"/>
-      <c r="G148" s="34" t="n"/>
-      <c r="H148" s="33" t="n"/>
-      <c r="I148" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J148" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K148" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L148" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M148" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" s="32" t="n"/>
-      <c r="C149" s="33" t="n"/>
-      <c r="D149" s="32" t="n"/>
-      <c r="E149" s="34" t="n"/>
-      <c r="F149" s="33" t="n"/>
-      <c r="G149" s="34" t="n"/>
-      <c r="H149" s="33" t="n"/>
-      <c r="I149" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J149" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K149" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L149" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M149" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="32" t="n"/>
-      <c r="C150" s="33" t="n"/>
-      <c r="D150" s="32" t="n"/>
-      <c r="E150" s="34" t="n"/>
-      <c r="F150" s="33" t="n"/>
-      <c r="G150" s="34" t="n"/>
-      <c r="H150" s="33" t="n"/>
-      <c r="I150" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J150" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K150" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L150" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M150" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="32" t="n"/>
-      <c r="C151" s="33" t="n"/>
-      <c r="D151" s="32" t="n"/>
-      <c r="E151" s="34" t="n"/>
-      <c r="F151" s="33" t="n"/>
-      <c r="G151" s="34" t="n"/>
-      <c r="H151" s="33" t="n"/>
-      <c r="I151" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J151" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K151" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L151" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M151" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="B152" s="32" t="n"/>
-      <c r="C152" s="33" t="n"/>
-      <c r="D152" s="32" t="n"/>
-      <c r="E152" s="34" t="n"/>
-      <c r="F152" s="33" t="n"/>
-      <c r="G152" s="34" t="n"/>
-      <c r="H152" s="33" t="n"/>
-      <c r="I152" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J152" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K152" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L152" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M152" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="B153" s="32" t="n"/>
-      <c r="C153" s="33" t="n"/>
-      <c r="D153" s="32" t="n"/>
-      <c r="E153" s="34" t="n"/>
-      <c r="F153" s="33" t="n"/>
-      <c r="G153" s="34" t="n"/>
-      <c r="H153" s="33" t="n"/>
-      <c r="I153" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J153" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K153" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L153" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M153" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="B154" s="32" t="n"/>
-      <c r="C154" s="33" t="n"/>
-      <c r="D154" s="32" t="n"/>
-      <c r="E154" s="34" t="n"/>
-      <c r="F154" s="33" t="n"/>
-      <c r="G154" s="34" t="n"/>
-      <c r="H154" s="33" t="n"/>
-      <c r="I154" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J154" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K154" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L154" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M154" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="B155" s="32" t="n"/>
-      <c r="C155" s="33" t="n"/>
-      <c r="D155" s="32" t="n"/>
-      <c r="E155" s="34" t="n"/>
-      <c r="F155" s="33" t="n"/>
-      <c r="G155" s="34" t="n"/>
-      <c r="H155" s="33" t="n"/>
-      <c r="I155" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J155" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K155" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L155" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M155" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="156">
-      <c r="B156" s="32" t="n"/>
-      <c r="C156" s="33" t="n"/>
-      <c r="D156" s="32" t="n"/>
-      <c r="E156" s="34" t="n"/>
-      <c r="F156" s="33" t="n"/>
-      <c r="G156" s="34" t="n"/>
-      <c r="H156" s="33" t="n"/>
-      <c r="I156" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J156" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K156" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L156" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M156" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157">
-      <c r="B157" s="32" t="n"/>
-      <c r="C157" s="33" t="n"/>
-      <c r="D157" s="32" t="n"/>
-      <c r="E157" s="34" t="n"/>
-      <c r="F157" s="33" t="n"/>
-      <c r="G157" s="34" t="n"/>
-      <c r="H157" s="33" t="n"/>
-      <c r="I157" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J157" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K157" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L157" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M157" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158">
-      <c r="B158" s="32" t="n"/>
-      <c r="C158" s="33" t="n"/>
-      <c r="D158" s="32" t="n"/>
-      <c r="E158" s="34" t="n"/>
-      <c r="F158" s="33" t="n"/>
-      <c r="G158" s="34" t="n"/>
-      <c r="H158" s="33" t="n"/>
-      <c r="I158" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J158" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K158" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L158" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M158" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159">
-      <c r="B159" s="32" t="n"/>
-      <c r="C159" s="33" t="n"/>
-      <c r="D159" s="32" t="n"/>
-      <c r="E159" s="34" t="n"/>
-      <c r="F159" s="33" t="n"/>
-      <c r="G159" s="34" t="n"/>
-      <c r="H159" s="33" t="n"/>
-      <c r="I159" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J159" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K159" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L159" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M159" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="B160" s="32" t="n"/>
-      <c r="C160" s="33" t="n"/>
-      <c r="D160" s="32" t="n"/>
-      <c r="E160" s="34" t="n"/>
-      <c r="F160" s="33" t="n"/>
-      <c r="G160" s="34" t="n"/>
-      <c r="H160" s="33" t="n"/>
-      <c r="I160" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J160" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K160" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L160" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M160" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161">
-      <c r="B161" s="32" t="n"/>
-      <c r="C161" s="33" t="n"/>
-      <c r="D161" s="32" t="n"/>
-      <c r="E161" s="34" t="n"/>
-      <c r="F161" s="33" t="n"/>
-      <c r="G161" s="34" t="n"/>
-      <c r="H161" s="33" t="n"/>
-      <c r="I161" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J161" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K161" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L161" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M161" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="B162" s="32" t="n"/>
-      <c r="C162" s="33" t="n"/>
-      <c r="D162" s="32" t="n"/>
-      <c r="E162" s="34" t="n"/>
-      <c r="F162" s="33" t="n"/>
-      <c r="G162" s="34" t="n"/>
-      <c r="H162" s="33" t="n"/>
-      <c r="I162" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J162" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K162" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L162" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M162" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163">
-      <c r="B163" s="32" t="n"/>
-      <c r="C163" s="33" t="n"/>
-      <c r="D163" s="32" t="n"/>
-      <c r="E163" s="34" t="n"/>
-      <c r="F163" s="33" t="n"/>
-      <c r="G163" s="34" t="n"/>
-      <c r="H163" s="33" t="n"/>
-      <c r="I163" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J163" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K163" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L163" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M163" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164">
-      <c r="B164" s="32" t="n"/>
-      <c r="C164" s="33" t="n"/>
-      <c r="D164" s="32" t="n"/>
-      <c r="E164" s="34" t="n"/>
-      <c r="F164" s="33" t="n"/>
-      <c r="G164" s="34" t="n"/>
-      <c r="H164" s="33" t="n"/>
-      <c r="I164" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J164" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K164" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L164" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M164" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="B165" s="32" t="n"/>
-      <c r="C165" s="33" t="n"/>
-      <c r="D165" s="32" t="n"/>
-      <c r="E165" s="34" t="n"/>
-      <c r="F165" s="33" t="n"/>
-      <c r="G165" s="34" t="n"/>
-      <c r="H165" s="33" t="n"/>
-      <c r="I165" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J165" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K165" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L165" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M165" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166">
-      <c r="B166" s="32" t="n"/>
-      <c r="C166" s="33" t="n"/>
-      <c r="D166" s="32" t="n"/>
-      <c r="E166" s="34" t="n"/>
-      <c r="F166" s="33" t="n"/>
-      <c r="G166" s="34" t="n"/>
-      <c r="H166" s="33" t="n"/>
-      <c r="I166" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J166" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K166" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L166" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M166" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167">
-      <c r="B167" s="32" t="n"/>
-      <c r="C167" s="33" t="n"/>
-      <c r="D167" s="32" t="n"/>
-      <c r="E167" s="34" t="n"/>
-      <c r="F167" s="33" t="n"/>
-      <c r="G167" s="34" t="n"/>
-      <c r="H167" s="33" t="n"/>
-      <c r="I167" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J167" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K167" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L167" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M167" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="B168" s="32" t="n"/>
-      <c r="C168" s="33" t="n"/>
-      <c r="D168" s="32" t="n"/>
-      <c r="E168" s="34" t="n"/>
-      <c r="F168" s="33" t="n"/>
-      <c r="G168" s="34" t="n"/>
-      <c r="H168" s="33" t="n"/>
-      <c r="I168" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J168" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K168" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L168" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M168" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="B169" s="32" t="n"/>
-      <c r="C169" s="33" t="n"/>
-      <c r="D169" s="32" t="n"/>
-      <c r="E169" s="34" t="n"/>
-      <c r="F169" s="33" t="n"/>
-      <c r="G169" s="34" t="n"/>
-      <c r="H169" s="33" t="n"/>
-      <c r="I169" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J169" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K169" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L169" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M169" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170">
-      <c r="B170" s="32" t="n"/>
-      <c r="C170" s="33" t="n"/>
-      <c r="D170" s="32" t="n"/>
-      <c r="E170" s="34" t="n"/>
-      <c r="F170" s="33" t="n"/>
-      <c r="G170" s="34" t="n"/>
-      <c r="H170" s="33" t="n"/>
-      <c r="I170" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J170" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K170" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L170" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M170" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="171">
-      <c r="B171" s="32" t="n"/>
-      <c r="C171" s="33" t="n"/>
-      <c r="D171" s="32" t="n"/>
-      <c r="E171" s="34" t="n"/>
-      <c r="F171" s="33" t="n"/>
-      <c r="G171" s="34" t="n"/>
-      <c r="H171" s="33" t="n"/>
-      <c r="I171" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J171" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K171" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L171" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M171" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172">
-      <c r="B172" s="32" t="n"/>
-      <c r="C172" s="33" t="n"/>
-      <c r="D172" s="32" t="n"/>
-      <c r="E172" s="34" t="n"/>
-      <c r="F172" s="33" t="n"/>
-      <c r="G172" s="34" t="n"/>
-      <c r="H172" s="33" t="n"/>
-      <c r="I172" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J172" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K172" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L172" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M172" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="B173" s="32" t="n"/>
-      <c r="C173" s="33" t="n"/>
-      <c r="D173" s="32" t="n"/>
-      <c r="E173" s="34" t="n"/>
-      <c r="F173" s="33" t="n"/>
-      <c r="G173" s="34" t="n"/>
-      <c r="H173" s="33" t="n"/>
-      <c r="I173" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J173" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K173" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L173" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M173" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="B174" s="32" t="n"/>
-      <c r="C174" s="33" t="n"/>
-      <c r="D174" s="32" t="n"/>
-      <c r="E174" s="34" t="n"/>
-      <c r="F174" s="33" t="n"/>
-      <c r="G174" s="34" t="n"/>
-      <c r="H174" s="33" t="n"/>
-      <c r="I174" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J174" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K174" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L174" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M174" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="B175" s="32" t="n"/>
-      <c r="C175" s="33" t="n"/>
-      <c r="D175" s="32" t="n"/>
-      <c r="E175" s="34" t="n"/>
-      <c r="F175" s="33" t="n"/>
-      <c r="G175" s="34" t="n"/>
-      <c r="H175" s="33" t="n"/>
-      <c r="I175" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J175" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K175" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L175" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M175" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="B176" s="32" t="n"/>
-      <c r="C176" s="33" t="n"/>
-      <c r="D176" s="32" t="n"/>
-      <c r="E176" s="34" t="n"/>
-      <c r="F176" s="33" t="n"/>
-      <c r="G176" s="34" t="n"/>
-      <c r="H176" s="33" t="n"/>
-      <c r="I176" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J176" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K176" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L176" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M176" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="B177" s="32" t="n"/>
-      <c r="C177" s="33" t="n"/>
-      <c r="D177" s="32" t="n"/>
-      <c r="E177" s="34" t="n"/>
-      <c r="F177" s="33" t="n"/>
-      <c r="G177" s="34" t="n"/>
-      <c r="H177" s="33" t="n"/>
-      <c r="I177" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J177" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K177" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L177" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M177" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="B178" s="32" t="n"/>
-      <c r="C178" s="33" t="n"/>
-      <c r="D178" s="32" t="n"/>
-      <c r="E178" s="34" t="n"/>
-      <c r="F178" s="33" t="n"/>
-      <c r="G178" s="34" t="n"/>
-      <c r="H178" s="33" t="n"/>
-      <c r="I178" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J178" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K178" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L178" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M178" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="B179" s="32" t="n"/>
-      <c r="C179" s="33" t="n"/>
-      <c r="D179" s="32" t="n"/>
-      <c r="E179" s="34" t="n"/>
-      <c r="F179" s="33" t="n"/>
-      <c r="G179" s="34" t="n"/>
-      <c r="H179" s="33" t="n"/>
-      <c r="I179" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J179" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K179" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L179" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M179" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="B180" s="32" t="n"/>
-      <c r="C180" s="33" t="n"/>
-      <c r="D180" s="32" t="n"/>
-      <c r="E180" s="34" t="n"/>
-      <c r="F180" s="33" t="n"/>
-      <c r="G180" s="34" t="n"/>
-      <c r="H180" s="33" t="n"/>
-      <c r="I180" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J180" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K180" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L180" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M180" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="B181" s="32" t="n"/>
-      <c r="C181" s="33" t="n"/>
-      <c r="D181" s="32" t="n"/>
-      <c r="E181" s="34" t="n"/>
-      <c r="F181" s="33" t="n"/>
-      <c r="G181" s="34" t="n"/>
-      <c r="H181" s="33" t="n"/>
-      <c r="I181" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J181" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K181" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L181" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M181" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="B182" s="32" t="n"/>
-      <c r="C182" s="33" t="n"/>
-      <c r="D182" s="32" t="n"/>
-      <c r="E182" s="34" t="n"/>
-      <c r="F182" s="33" t="n"/>
-      <c r="G182" s="34" t="n"/>
-      <c r="H182" s="33" t="n"/>
-      <c r="I182" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J182" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K182" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L182" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M182" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="B183" s="32" t="n"/>
-      <c r="C183" s="33" t="n"/>
-      <c r="D183" s="32" t="n"/>
-      <c r="E183" s="34" t="n"/>
-      <c r="F183" s="33" t="n"/>
-      <c r="G183" s="34" t="n"/>
-      <c r="H183" s="33" t="n"/>
-      <c r="I183" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J183" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K183" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L183" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M183" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="B184" s="32" t="n"/>
-      <c r="C184" s="33" t="n"/>
-      <c r="D184" s="32" t="n"/>
-      <c r="E184" s="34" t="n"/>
-      <c r="F184" s="33" t="n"/>
-      <c r="G184" s="34" t="n"/>
-      <c r="H184" s="33" t="n"/>
-      <c r="I184" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J184" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K184" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L184" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M184" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="B185" s="32" t="n"/>
-      <c r="C185" s="33" t="n"/>
-      <c r="D185" s="32" t="n"/>
-      <c r="E185" s="34" t="n"/>
-      <c r="F185" s="33" t="n"/>
-      <c r="G185" s="34" t="n"/>
-      <c r="H185" s="33" t="n"/>
-      <c r="I185" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J185" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K185" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L185" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M185" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="B186" s="32" t="n"/>
-      <c r="C186" s="33" t="n"/>
-      <c r="D186" s="32" t="n"/>
-      <c r="E186" s="34" t="n"/>
-      <c r="F186" s="33" t="n"/>
-      <c r="G186" s="34" t="n"/>
-      <c r="H186" s="33" t="n"/>
-      <c r="I186" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J186" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K186" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L186" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M186" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="B187" s="32" t="n"/>
-      <c r="C187" s="33" t="n"/>
-      <c r="D187" s="32" t="n"/>
-      <c r="E187" s="34" t="n"/>
-      <c r="F187" s="33" t="n"/>
-      <c r="G187" s="34" t="n"/>
-      <c r="H187" s="33" t="n"/>
-      <c r="I187" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J187" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K187" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L187" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M187" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="B188" s="32" t="n"/>
-      <c r="C188" s="33" t="n"/>
-      <c r="D188" s="32" t="n"/>
-      <c r="E188" s="34" t="n"/>
-      <c r="F188" s="33" t="n"/>
-      <c r="G188" s="34" t="n"/>
-      <c r="H188" s="33" t="n"/>
-      <c r="I188" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J188" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K188" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L188" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M188" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="B189" s="32" t="n"/>
-      <c r="C189" s="33" t="n"/>
-      <c r="D189" s="32" t="n"/>
-      <c r="E189" s="34" t="n"/>
-      <c r="F189" s="33" t="n"/>
-      <c r="G189" s="34" t="n"/>
-      <c r="H189" s="33" t="n"/>
-      <c r="I189" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J189" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K189" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L189" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M189" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="B190" s="32" t="n"/>
-      <c r="C190" s="33" t="n"/>
-      <c r="D190" s="32" t="n"/>
-      <c r="E190" s="34" t="n"/>
-      <c r="F190" s="33" t="n"/>
-      <c r="G190" s="34" t="n"/>
-      <c r="H190" s="33" t="n"/>
-      <c r="I190" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J190" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K190" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L190" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M190" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="B191" s="32" t="n"/>
-      <c r="C191" s="33" t="n"/>
-      <c r="D191" s="32" t="n"/>
-      <c r="E191" s="34" t="n"/>
-      <c r="F191" s="33" t="n"/>
-      <c r="G191" s="34" t="n"/>
-      <c r="H191" s="33" t="n"/>
-      <c r="I191" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J191" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K191" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L191" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M191" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="B192" s="32" t="n"/>
-      <c r="C192" s="33" t="n"/>
-      <c r="D192" s="32" t="n"/>
-      <c r="E192" s="34" t="n"/>
-      <c r="F192" s="33" t="n"/>
-      <c r="G192" s="34" t="n"/>
-      <c r="H192" s="33" t="n"/>
-      <c r="I192" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J192" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K192" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L192" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M192" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="B193" s="32" t="n"/>
-      <c r="C193" s="33" t="n"/>
-      <c r="D193" s="32" t="n"/>
-      <c r="E193" s="34" t="n"/>
-      <c r="F193" s="33" t="n"/>
-      <c r="G193" s="34" t="n"/>
-      <c r="H193" s="33" t="n"/>
-      <c r="I193" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J193" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K193" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L193" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M193" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="B194" s="32" t="n"/>
-      <c r="C194" s="33" t="n"/>
-      <c r="D194" s="32" t="n"/>
-      <c r="E194" s="34" t="n"/>
-      <c r="F194" s="33" t="n"/>
-      <c r="G194" s="34" t="n"/>
-      <c r="H194" s="33" t="n"/>
-      <c r="I194" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J194" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K194" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L194" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M194" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="B195" s="32" t="n"/>
-      <c r="C195" s="33" t="n"/>
-      <c r="D195" s="32" t="n"/>
-      <c r="E195" s="34" t="n"/>
-      <c r="F195" s="33" t="n"/>
-      <c r="G195" s="34" t="n"/>
-      <c r="H195" s="33" t="n"/>
-      <c r="I195" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J195" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K195" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L195" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M195" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="B196" s="32" t="n"/>
-      <c r="C196" s="33" t="n"/>
-      <c r="D196" s="32" t="n"/>
-      <c r="E196" s="34" t="n"/>
-      <c r="F196" s="33" t="n"/>
-      <c r="G196" s="34" t="n"/>
-      <c r="H196" s="33" t="n"/>
-      <c r="I196" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J196" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K196" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L196" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M196" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="B197" s="32" t="n"/>
-      <c r="C197" s="33" t="n"/>
-      <c r="D197" s="32" t="n"/>
-      <c r="E197" s="34" t="n"/>
-      <c r="F197" s="33" t="n"/>
-      <c r="G197" s="34" t="n"/>
-      <c r="H197" s="33" t="n"/>
-      <c r="I197" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J197" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K197" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L197" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M197" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="B198" s="32" t="n"/>
-      <c r="C198" s="33" t="n"/>
-      <c r="D198" s="32" t="n"/>
-      <c r="E198" s="34" t="n"/>
-      <c r="F198" s="33" t="n"/>
-      <c r="G198" s="34" t="n"/>
-      <c r="H198" s="33" t="n"/>
-      <c r="I198" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J198" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K198" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L198" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M198" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="B199" s="32" t="n"/>
-      <c r="C199" s="33" t="n"/>
-      <c r="D199" s="32" t="n"/>
-      <c r="E199" s="34" t="n"/>
-      <c r="F199" s="33" t="n"/>
-      <c r="G199" s="34" t="n"/>
-      <c r="H199" s="33" t="n"/>
-      <c r="I199" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J199" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K199" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L199" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M199" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200">
-      <c r="B200" s="32" t="n"/>
-      <c r="C200" s="33" t="n"/>
-      <c r="D200" s="32" t="n"/>
-      <c r="E200" s="34" t="n"/>
-      <c r="F200" s="33" t="n"/>
-      <c r="G200" s="34" t="n"/>
-      <c r="H200" s="33" t="n"/>
-      <c r="I200" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J200" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K200" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L200" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M200" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201">
-      <c r="B201" s="32" t="n"/>
-      <c r="C201" s="33" t="n"/>
-      <c r="D201" s="32" t="n"/>
-      <c r="E201" s="34" t="n"/>
-      <c r="F201" s="33" t="n"/>
-      <c r="G201" s="34" t="n"/>
-      <c r="H201" s="33" t="n"/>
-      <c r="I201" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J201" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K201" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L201" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M201" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202">
-      <c r="B202" s="32" t="n"/>
-      <c r="C202" s="33" t="n"/>
-      <c r="D202" s="32" t="n"/>
-      <c r="E202" s="34" t="n"/>
-      <c r="F202" s="33" t="n"/>
-      <c r="G202" s="34" t="n"/>
-      <c r="H202" s="33" t="n"/>
-      <c r="I202" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J202" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K202" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L202" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M202" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="B203" s="32" t="n"/>
-      <c r="C203" s="33" t="n"/>
-      <c r="D203" s="32" t="n"/>
-      <c r="E203" s="34" t="n"/>
-      <c r="F203" s="33" t="n"/>
-      <c r="G203" s="34" t="n"/>
-      <c r="H203" s="33" t="n"/>
-      <c r="I203" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J203" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K203" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L203" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M203" s="29">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204">
-      <c r="B204" s="32" t="n"/>
-      <c r="C204" s="33" t="n"/>
-      <c r="D204" s="32" t="n"/>
-      <c r="E204" s="34" t="n"/>
-      <c r="F204" s="33" t="n"/>
-      <c r="G204" s="34" t="n"/>
-      <c r="H204" s="33" t="n"/>
-      <c r="I204" s="22">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J204" s="22">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K204" s="27">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L204" s="29">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M204" s="29">
+      <c r="B124" s="38" t="n"/>
+      <c r="D124" s="38" t="n"/>
+      <c r="I124" s="35">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J124" s="35">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K124" s="36">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L124" s="37">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M124" s="37">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:M204"/>
-  <conditionalFormatting sqref="K5:K204">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="10">
+  <autoFilter ref="B4:M124"/>
+  <conditionalFormatting sqref="B5:H124">
+    <cfRule type="expression" priority="1" dxfId="11">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K5:K124">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="10">
       <formula>"要確認"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="9">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="9">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G204">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="3">
+  <conditionalFormatting sqref="G5:G124">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"申請中"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="9">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="9">
       <formula>"承認"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
       <formula>"却下"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="C5:C204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=STAFF_NAMES</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=設定!$B$30:$B$38</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G124" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"申請中,承認,却下"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5:B204 D5:D204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="日付を 2026/9/10 の形式で入力してください" type="date" operator="greaterThan">
+    <dataValidation sqref="B5:B124 D5:D124" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="日付を 2026/9/10 の形式で入力してください" type="date" operator="greaterThan">
       <formula1>40000</formula1>
     </dataValidation>
   </dataValidations>
@@ -10998,10 +8118,10 @@
       <c r="D5" s="32" t="n">
         <v>46113</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="39" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="23">
@@ -11016,7 +8136,7 @@
         <f t="shared" ref="I5:I10" si="4">IF(B5="","",IF(C5="派遣","対象外（派遣元）",IF(E5&gt;=10,IF(G5&gt;=5,"達成","あと"&amp;(5-G5)&amp;"日"),"対象外")))</f>
         <v/>
       </c>
-      <c r="J5" s="36" t="inlineStr">
+      <c r="J5" s="40" t="inlineStr">
         <is>
           <t>付与日数・繰越は例。実際の値に直す。</t>
         </is>
@@ -11034,10 +8154,10 @@
       <c r="D6" s="32" t="n">
         <v>46113</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="39" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="23">
@@ -11052,7 +8172,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J6" s="36" t="inlineStr"/>
+      <c r="J6" s="40" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="19">
@@ -11064,8 +8184,8 @@
         <v/>
       </c>
       <c r="D7" s="32" t="n"/>
-      <c r="E7" s="35" t="n"/>
-      <c r="F7" s="35" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
       <c r="G7" s="23">
         <f t="shared" si="2"/>
         <v/>
@@ -11078,7 +8198,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J7" s="36" t="inlineStr"/>
+      <c r="J7" s="40" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="19">
@@ -11090,8 +8210,8 @@
         <v/>
       </c>
       <c r="D8" s="32" t="n"/>
-      <c r="E8" s="35" t="n"/>
-      <c r="F8" s="35" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
       <c r="G8" s="23">
         <f t="shared" si="2"/>
         <v/>
@@ -11104,7 +8224,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J8" s="36" t="inlineStr"/>
+      <c r="J8" s="40" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="19">
@@ -11116,8 +8236,8 @@
         <v/>
       </c>
       <c r="D9" s="32" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
       <c r="G9" s="23">
         <f t="shared" si="2"/>
         <v/>
@@ -11130,7 +8250,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J9" s="36" t="inlineStr"/>
+      <c r="J9" s="40" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="19">
@@ -11142,8 +8262,8 @@
         <v/>
       </c>
       <c r="D10" s="32" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
       <c r="G10" s="23">
         <f t="shared" si="2"/>
         <v/>
@@ -11156,7 +8276,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J10" s="36" t="inlineStr"/>
+      <c r="J10" s="40" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I5:I10">
@@ -11168,7 +8288,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5:H10">
-    <cfRule type="expression" priority="3" dxfId="11">
+    <cfRule type="expression" priority="3" dxfId="12">
       <formula>AND(ISNUMBER(H5),H5&lt;=2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11218,12 +8338,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>メンバー（氏名・区分・勤務曜日）</t>
         </is>
       </c>
-      <c r="N3" s="37" t="inlineStr">
+      <c r="N3" s="41" t="inlineStr">
         <is>
           <t>祝日・会社休業日（追加可）</t>
         </is>
@@ -11337,7 +8457,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="K5" s="36" t="inlineStr">
+      <c r="K5" s="40" t="inlineStr">
         <is>
           <t>氏名を書き換える</t>
         </is>
@@ -11397,7 +8517,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="K6" s="36" t="inlineStr"/>
+      <c r="K6" s="40" t="inlineStr"/>
       <c r="N6" s="32" t="n">
         <v>46287</v>
       </c>
@@ -11453,7 +8573,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="K7" s="36" t="inlineStr">
+      <c r="K7" s="40" t="inlineStr">
         <is>
           <t>契約勤務日に合わせて○×を直す</t>
         </is>
@@ -11513,7 +8633,7 @@
           <t>×</t>
         </is>
       </c>
-      <c r="K8" s="36" t="inlineStr"/>
+      <c r="K8" s="40" t="inlineStr"/>
       <c r="N8" s="32" t="n">
         <v>46307</v>
       </c>
@@ -11533,7 +8653,7 @@
       <c r="H9" s="34" t="inlineStr"/>
       <c r="I9" s="34" t="inlineStr"/>
       <c r="J9" s="34" t="inlineStr"/>
-      <c r="K9" s="36" t="inlineStr"/>
+      <c r="K9" s="40" t="inlineStr"/>
       <c r="N9" s="32" t="n">
         <v>46329</v>
       </c>
@@ -11553,7 +8673,7 @@
       <c r="H10" s="34" t="inlineStr"/>
       <c r="I10" s="34" t="inlineStr"/>
       <c r="J10" s="34" t="inlineStr"/>
-      <c r="K10" s="36" t="inlineStr"/>
+      <c r="K10" s="40" t="inlineStr"/>
       <c r="N10" s="32" t="n">
         <v>46349</v>
       </c>
@@ -11574,7 +8694,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>ルール（人数の下限）</t>
         </is>
@@ -11609,7 +8729,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>最低出勤人数（1日あたり）</t>
         </is>
@@ -11627,7 +8747,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>最低正社員出勤人数</t>
         </is>
@@ -11645,7 +8765,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>申請期限の目安</t>
         </is>
@@ -11683,7 +8803,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>営業曜日（×の曜日は休業日として全員カウント対象外）</t>
         </is>
@@ -11868,7 +8988,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>記号（休暇申請の種別）</t>
         </is>
@@ -11919,21 +9039,21 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
-      <c r="C30" s="38" t="inlineStr">
+      <c r="C30" s="42" t="inlineStr">
         <is>
           <t>有給休暇</t>
         </is>
       </c>
-      <c r="D30" s="40" t="n">
+      <c r="D30" s="44" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="5" t="n"/>
-      <c r="F30" s="41" t="inlineStr">
+      <c r="F30" s="45" t="inlineStr">
         <is>
           <t>正社員は年5日取得義務の対象</t>
         </is>
@@ -11953,21 +9073,21 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="39" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>午前</t>
         </is>
       </c>
-      <c r="C31" s="38" t="inlineStr">
+      <c r="C31" s="42" t="inlineStr">
         <is>
           <t>午前半休</t>
         </is>
       </c>
-      <c r="D31" s="40" t="n">
+      <c r="D31" s="44" t="n">
         <v>0.5</v>
       </c>
       <c r="E31" s="5" t="n"/>
-      <c r="F31" s="41" t="inlineStr">
+      <c r="F31" s="45" t="inlineStr">
         <is>
           <t>0.5日の有給として集計</t>
         </is>
@@ -11987,21 +9107,21 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>午後</t>
         </is>
       </c>
-      <c r="C32" s="38" t="inlineStr">
+      <c r="C32" s="42" t="inlineStr">
         <is>
           <t>午後半休</t>
         </is>
       </c>
-      <c r="D32" s="40" t="n">
+      <c r="D32" s="44" t="n">
         <v>0.5</v>
       </c>
       <c r="E32" s="5" t="n"/>
-      <c r="F32" s="41" t="inlineStr">
+      <c r="F32" s="45" t="inlineStr">
         <is>
           <t>0.5日の有給として集計</t>
         </is>
@@ -12011,25 +9131,25 @@
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="5" t="n"/>
-      <c r="N32" s="42" t="n"/>
+      <c r="N32" s="46" t="n"/>
       <c r="O32" s="33" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="39" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="C33" s="38" t="inlineStr">
+      <c r="C33" s="42" t="inlineStr">
         <is>
           <t>公休・希望休</t>
         </is>
       </c>
-      <c r="D33" s="40" t="n">
+      <c r="D33" s="44" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="5" t="n"/>
-      <c r="F33" s="41" t="inlineStr">
+      <c r="F33" s="45" t="inlineStr">
         <is>
           <t>無給の休み・シフト調整による休み</t>
         </is>
@@ -12039,73 +9159,73 @@
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="5" t="n"/>
-      <c r="N33" s="42" t="n"/>
+      <c r="N33" s="46" t="n"/>
       <c r="O33" s="33" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="39" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>特</t>
         </is>
       </c>
-      <c r="C34" s="38" t="inlineStr">
+      <c r="C34" s="42" t="inlineStr">
         <is>
           <t>特別休暇（慶弔など）</t>
         </is>
       </c>
-      <c r="D34" s="40" t="n">
+      <c r="D34" s="44" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="5" t="n"/>
-      <c r="F34" s="41" t="inlineStr"/>
+      <c r="F34" s="45" t="inlineStr"/>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="5" t="n"/>
-      <c r="N34" s="42" t="n"/>
+      <c r="N34" s="46" t="n"/>
       <c r="O34" s="33" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="39" t="inlineStr">
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>代</t>
         </is>
       </c>
-      <c r="C35" s="38" t="inlineStr">
+      <c r="C35" s="42" t="inlineStr">
         <is>
           <t>代休・振替休日</t>
         </is>
       </c>
-      <c r="D35" s="40" t="n">
+      <c r="D35" s="44" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="5" t="n"/>
-      <c r="F35" s="41" t="inlineStr"/>
+      <c r="F35" s="45" t="inlineStr"/>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="5" t="n"/>
-      <c r="N35" s="42" t="n"/>
+      <c r="N35" s="46" t="n"/>
       <c r="O35" s="33" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>欠</t>
         </is>
       </c>
-      <c r="C36" s="38" t="inlineStr">
+      <c r="C36" s="42" t="inlineStr">
         <is>
           <t>欠勤</t>
         </is>
       </c>
-      <c r="D36" s="40" t="n">
+      <c r="D36" s="44" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="5" t="n"/>
-      <c r="F36" s="41" t="inlineStr">
+      <c r="F36" s="45" t="inlineStr">
         <is>
           <t>事後登録用</t>
         </is>
@@ -12115,25 +9235,25 @@
       <c r="I36" s="6" t="n"/>
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="5" t="n"/>
-      <c r="N36" s="42" t="n"/>
+      <c r="N36" s="46" t="n"/>
       <c r="O36" s="33" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="39" t="inlineStr">
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>在</t>
         </is>
       </c>
-      <c r="C37" s="38" t="inlineStr">
+      <c r="C37" s="42" t="inlineStr">
         <is>
           <t>在宅勤務</t>
         </is>
       </c>
-      <c r="D37" s="40" t="n">
+      <c r="D37" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E37" s="5" t="n"/>
-      <c r="F37" s="41" t="inlineStr">
+      <c r="F37" s="45" t="inlineStr">
         <is>
           <t>出勤扱い。所在把握のために記録</t>
         </is>
@@ -12143,25 +9263,25 @@
       <c r="I37" s="6" t="n"/>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="5" t="n"/>
-      <c r="N37" s="42" t="n"/>
+      <c r="N37" s="46" t="n"/>
       <c r="O37" s="33" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="39" t="inlineStr">
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>外</t>
         </is>
       </c>
-      <c r="C38" s="38" t="inlineStr">
+      <c r="C38" s="42" t="inlineStr">
         <is>
           <t>外出・出張</t>
         </is>
       </c>
-      <c r="D38" s="40" t="n">
+      <c r="D38" s="44" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="5" t="n"/>
-      <c r="F38" s="41" t="inlineStr">
+      <c r="F38" s="45" t="inlineStr">
         <is>
           <t>出勤扱い。事務所に人がいない場合は別途注意</t>
         </is>
@@ -12171,175 +9291,175 @@
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="5" t="n"/>
-      <c r="N38" s="42" t="n"/>
+      <c r="N38" s="46" t="n"/>
       <c r="O38" s="33" t="n"/>
     </row>
     <row r="39">
-      <c r="N39" s="42" t="n"/>
+      <c r="N39" s="46" t="n"/>
       <c r="O39" s="33" t="n"/>
     </row>
     <row r="40">
-      <c r="N40" s="42" t="n"/>
+      <c r="N40" s="46" t="n"/>
       <c r="O40" s="33" t="n"/>
     </row>
     <row r="41">
-      <c r="N41" s="42" t="n"/>
+      <c r="N41" s="46" t="n"/>
       <c r="O41" s="33" t="n"/>
     </row>
     <row r="42">
-      <c r="N42" s="42" t="n"/>
+      <c r="N42" s="46" t="n"/>
       <c r="O42" s="33" t="n"/>
     </row>
     <row r="43">
-      <c r="N43" s="42" t="n"/>
+      <c r="N43" s="46" t="n"/>
       <c r="O43" s="33" t="n"/>
     </row>
     <row r="44">
-      <c r="N44" s="42" t="n"/>
+      <c r="N44" s="46" t="n"/>
       <c r="O44" s="33" t="n"/>
     </row>
     <row r="45">
-      <c r="N45" s="42" t="n"/>
+      <c r="N45" s="46" t="n"/>
       <c r="O45" s="33" t="n"/>
     </row>
     <row r="46">
-      <c r="N46" s="42" t="n"/>
+      <c r="N46" s="46" t="n"/>
       <c r="O46" s="33" t="n"/>
     </row>
     <row r="47">
-      <c r="N47" s="42" t="n"/>
+      <c r="N47" s="46" t="n"/>
       <c r="O47" s="33" t="n"/>
     </row>
     <row r="48">
-      <c r="N48" s="42" t="n"/>
+      <c r="N48" s="46" t="n"/>
       <c r="O48" s="33" t="n"/>
     </row>
     <row r="49">
-      <c r="N49" s="42" t="n"/>
+      <c r="N49" s="46" t="n"/>
       <c r="O49" s="33" t="n"/>
     </row>
     <row r="50">
-      <c r="N50" s="42" t="n"/>
+      <c r="N50" s="46" t="n"/>
       <c r="O50" s="33" t="n"/>
     </row>
     <row r="51">
-      <c r="N51" s="42" t="n"/>
+      <c r="N51" s="46" t="n"/>
       <c r="O51" s="33" t="n"/>
     </row>
     <row r="52">
-      <c r="N52" s="42" t="n"/>
+      <c r="N52" s="46" t="n"/>
       <c r="O52" s="33" t="n"/>
     </row>
     <row r="53">
-      <c r="N53" s="42" t="n"/>
+      <c r="N53" s="46" t="n"/>
       <c r="O53" s="33" t="n"/>
     </row>
     <row r="54">
-      <c r="N54" s="42" t="n"/>
+      <c r="N54" s="46" t="n"/>
       <c r="O54" s="33" t="n"/>
     </row>
     <row r="55">
-      <c r="N55" s="42" t="n"/>
+      <c r="N55" s="46" t="n"/>
       <c r="O55" s="33" t="n"/>
     </row>
     <row r="56">
-      <c r="N56" s="42" t="n"/>
+      <c r="N56" s="46" t="n"/>
       <c r="O56" s="33" t="n"/>
     </row>
     <row r="57">
-      <c r="N57" s="42" t="n"/>
+      <c r="N57" s="46" t="n"/>
       <c r="O57" s="33" t="n"/>
     </row>
     <row r="58">
-      <c r="N58" s="42" t="n"/>
+      <c r="N58" s="46" t="n"/>
       <c r="O58" s="33" t="n"/>
     </row>
     <row r="59">
-      <c r="N59" s="42" t="n"/>
+      <c r="N59" s="46" t="n"/>
       <c r="O59" s="33" t="n"/>
     </row>
     <row r="60">
-      <c r="N60" s="42" t="n"/>
+      <c r="N60" s="46" t="n"/>
       <c r="O60" s="33" t="n"/>
     </row>
     <row r="61">
-      <c r="N61" s="42" t="n"/>
+      <c r="N61" s="46" t="n"/>
       <c r="O61" s="33" t="n"/>
     </row>
     <row r="62">
-      <c r="N62" s="42" t="n"/>
+      <c r="N62" s="46" t="n"/>
       <c r="O62" s="33" t="n"/>
     </row>
     <row r="63">
-      <c r="N63" s="42" t="n"/>
+      <c r="N63" s="46" t="n"/>
       <c r="O63" s="33" t="n"/>
     </row>
     <row r="64">
-      <c r="N64" s="42" t="n"/>
+      <c r="N64" s="46" t="n"/>
       <c r="O64" s="33" t="n"/>
     </row>
     <row r="65">
-      <c r="N65" s="42" t="n"/>
+      <c r="N65" s="46" t="n"/>
       <c r="O65" s="33" t="n"/>
     </row>
     <row r="66">
-      <c r="N66" s="42" t="n"/>
+      <c r="N66" s="46" t="n"/>
       <c r="O66" s="33" t="n"/>
     </row>
     <row r="67">
-      <c r="N67" s="42" t="n"/>
+      <c r="N67" s="46" t="n"/>
       <c r="O67" s="33" t="n"/>
     </row>
     <row r="68">
-      <c r="N68" s="42" t="n"/>
+      <c r="N68" s="46" t="n"/>
       <c r="O68" s="33" t="n"/>
     </row>
     <row r="69">
-      <c r="N69" s="42" t="n"/>
+      <c r="N69" s="46" t="n"/>
       <c r="O69" s="33" t="n"/>
     </row>
     <row r="70">
-      <c r="N70" s="42" t="n"/>
+      <c r="N70" s="46" t="n"/>
       <c r="O70" s="33" t="n"/>
     </row>
     <row r="71">
-      <c r="N71" s="42" t="n"/>
+      <c r="N71" s="46" t="n"/>
       <c r="O71" s="33" t="n"/>
     </row>
     <row r="72">
-      <c r="N72" s="42" t="n"/>
+      <c r="N72" s="46" t="n"/>
       <c r="O72" s="33" t="n"/>
     </row>
     <row r="73">
-      <c r="N73" s="42" t="n"/>
+      <c r="N73" s="46" t="n"/>
       <c r="O73" s="33" t="n"/>
     </row>
     <row r="74">
-      <c r="N74" s="42" t="n"/>
+      <c r="N74" s="46" t="n"/>
       <c r="O74" s="33" t="n"/>
     </row>
     <row r="75">
-      <c r="N75" s="42" t="n"/>
+      <c r="N75" s="46" t="n"/>
       <c r="O75" s="33" t="n"/>
     </row>
     <row r="76">
-      <c r="N76" s="42" t="n"/>
+      <c r="N76" s="46" t="n"/>
       <c r="O76" s="33" t="n"/>
     </row>
     <row r="77">
-      <c r="N77" s="42" t="n"/>
+      <c r="N77" s="46" t="n"/>
       <c r="O77" s="33" t="n"/>
     </row>
     <row r="78">
-      <c r="N78" s="42" t="n"/>
+      <c r="N78" s="46" t="n"/>
       <c r="O78" s="33" t="n"/>
     </row>
     <row r="79">
-      <c r="N79" s="42" t="n"/>
+      <c r="N79" s="46" t="n"/>
       <c r="O79" s="33" t="n"/>
     </row>
     <row r="80">
-      <c r="N80" s="42" t="n"/>
+      <c r="N80" s="46" t="n"/>
       <c r="O80" s="33" t="n"/>
     </row>
   </sheetData>
@@ -12409,237 +9529,237 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="43" t="n"/>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="B4" s="47" t="n"/>
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>■ 基本の考え方</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>・入力するのは「休暇申請」シートだけ。1休暇につき1行（連休は日ごとに1行ずつ）。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="45" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>・「シフト表」は年・月を切り替えるだけで自動で組み上がる。手入力はしない。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="45" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>・「有給管理」は承認済みの申請から自動集計。付与日と付与日数だけ最初に入れる。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>・黄色のセル = 入力する場所。灰色のセル = 自動計算（触らない）。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="45" t="inlineStr"/>
+      <c r="C9" s="49" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="43" t="n"/>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="B10" s="47" t="n"/>
+      <c r="C10" s="48" t="inlineStr">
         <is>
           <t>■ 最初にやること（5分）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="45" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>1. 「設定」シートでメンバー4名の氏名・区分（正社員／派遣）・勤務曜日（○×）を入れる。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="45" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>2. 「設定」の最低出勤人数（初期値 2名）と、最低正社員出勤人数（初期値 1名）を確認する。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="45" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>3. 「有給管理」に各人の付与日・付与日数・繰越を入れる（派遣の残数は派遣元管理なので不要）。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>4. サンプルとして入っている申請4行（9/10に3人が重なって「要確認」が出る例）は削除してよい。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="45" t="inlineStr"/>
+      <c r="C15" s="49" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" s="43" t="n"/>
-      <c r="C16" s="44" t="inlineStr">
+      <c r="B16" s="47" t="n"/>
+      <c r="C16" s="48" t="inlineStr">
         <is>
           <t>■ 休みを取りたいとき（申請者）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="45" t="inlineStr">
+      <c r="C17" s="49" t="inlineStr">
         <is>
           <t>1. 「休暇申請」に 申請日・氏名・休暇日・種別・理由 を1行追加する。状態は「申請中」。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="45" t="inlineStr">
+      <c r="C18" s="49" t="inlineStr">
         <is>
           <t>2. 右側の「判定」列に「要確認」と出たら、その日は既に誰かが休む予定。日程をずらせないか先に相談する。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="45" t="inlineStr">
+      <c r="C19" s="49" t="inlineStr">
         <is>
           <t>3. 「シフト表」でも申請中の休みは (有) のようにカッコ付きで表示される。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="45" t="inlineStr"/>
+      <c r="C20" s="49" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="B21" s="43" t="n"/>
-      <c r="C21" s="44" t="inlineStr">
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="48" t="inlineStr">
         <is>
           <t>■ 承認するとき（管理者）</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="45" t="inlineStr">
+      <c r="C22" s="49" t="inlineStr">
         <is>
           <t>1. 「シフト表」の「申請中を承認した場合の判定」行を見る。「要注意」なら承認すると最低人数を割る。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="45" t="inlineStr">
+      <c r="C23" s="49" t="inlineStr">
         <is>
           <t>2. 問題なければ「休暇申請」の状態を「承認」に変え、承認者名を入れる。却下なら「却下」。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="45" t="inlineStr">
+      <c r="C24" s="49" t="inlineStr">
         <is>
           <t>3. 派遣メンバーの休みは、承認と同時に派遣元（派遣会社）にも連絡する。派遣元にとっては勤怠実績＝請求根拠。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="45" t="inlineStr"/>
+      <c r="C25" s="49" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="43" t="n"/>
-      <c r="C26" s="44" t="inlineStr">
+      <c r="B26" s="47" t="n"/>
+      <c r="C26" s="48" t="inlineStr">
         <is>
           <t>■ 運用ルールの例（設定シートで文言を変えられる）</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="45" t="inlineStr">
+      <c r="C27" s="49" t="inlineStr">
         <is>
           <t>・申請は原則、休みたい日の1週間前まで。急な体調不良は当日連絡＋事後に「欠」または「有」で登録。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="45" t="inlineStr">
+      <c r="C28" s="49" t="inlineStr">
         <is>
           <t>・同じ日に希望が重なったら「先に申請した人」ではなく「直近3か月の休み取得日数が少ない人」を優先すると不公平感が出にくい。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="45" t="inlineStr">
+      <c r="C29" s="49" t="inlineStr">
         <is>
           <t>・派遣2名だけの出勤日は作らない（指揮命令者が不在になる）。最低正社員出勤人数=1 はそのための設定。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="45" t="inlineStr">
+      <c r="C30" s="49" t="inlineStr">
         <is>
           <t>・正社員は年5日の有給取得義務あり。「有給管理」の「年5日義務」列が「あと○日」のままなら、管理者側から取得日を提案する。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="45" t="inlineStr"/>
+      <c r="C31" s="49" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="B32" s="43" t="n"/>
-      <c r="C32" s="44" t="inlineStr">
+      <c r="B32" s="47" t="n"/>
+      <c r="C32" s="48" t="inlineStr">
         <is>
           <t>■ 記号の意味</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="45" t="inlineStr">
+      <c r="C33" s="49" t="inlineStr">
         <is>
           <t>有=有給 / 午前=午前半休 / 午後=午後半休 / 休=公休・希望休 / 欠=欠勤 / 特=特別休暇 / 代=代休 / 在=在宅勤務 / 外=外出・出張</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="45" t="inlineStr">
+      <c r="C34" s="49" t="inlineStr">
         <is>
           <t>空欄=通常出勤、－=その人の勤務曜日ではない日、灰色の列=会社の休業日（土日祝）</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="45" t="inlineStr"/>
+      <c r="C35" s="49" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="B36" s="43" t="n"/>
-      <c r="C36" s="44" t="inlineStr">
+      <c r="B36" s="47" t="n"/>
+      <c r="C36" s="48" t="inlineStr">
         <is>
           <t>■ 注意</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="45" t="inlineStr">
+      <c r="C37" s="49" t="inlineStr">
         <is>
           <t>・シフト表は同時に1か月しか表示しない。過去月を見たいときは年・月を戻すだけでよい（データは休暇申請に残っている）。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="45" t="inlineStr">
+      <c r="C38" s="49" t="inlineStr">
         <is>
           <t>・休暇申請の日付は必ず日付形式（2026/9/10 のように入力）。文字として入ると集計に乗らない。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="45" t="inlineStr">
-        <is>
-          <t>・「休暇申請」の自動列（灰色）は200行分だけ式が入っている。それを超える場合は上の行をコピーする。</t>
+      <c r="C39" s="49" t="inlineStr">
+        <is>
+          <t>・「休暇申請」の自動列（灰色）は120行分だけ式が入っている。それを超える場合は上の行をコピーする。</t>
         </is>
       </c>
     </row>

--- a/attendance/勤怠管理_休暇調整シート.xlsx
+++ b/attendance/勤怠管理_休暇調整シート.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -276,21 +276,21 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="167" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -311,8 +311,8 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -320,6 +320,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -979,39 +982,129 @@
         </is>
       </c>
       <c r="D5" s="14">
-        <f t="array" ref="D5:AH5">IF(DATE($C$3,$E$3,1)+COLUMN(D$5:AH$5)-COLUMN($D$5)&gt;EOMONTH(DATE($C$3,$E$3,1),0),"",DATE($C$3,$E$3,1)+COLUMN(D$5:AH$5)-COLUMN($D$5))</f>
-        <v/>
-      </c>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="n"/>
-      <c r="I5" s="14" t="n"/>
-      <c r="J5" s="14" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="14" t="n"/>
-      <c r="M5" s="14" t="n"/>
-      <c r="N5" s="14" t="n"/>
-      <c r="O5" s="14" t="n"/>
-      <c r="P5" s="14" t="n"/>
-      <c r="Q5" s="14" t="n"/>
-      <c r="R5" s="14" t="n"/>
-      <c r="S5" s="14" t="n"/>
-      <c r="T5" s="14" t="n"/>
-      <c r="U5" s="14" t="n"/>
-      <c r="V5" s="14" t="n"/>
-      <c r="W5" s="14" t="n"/>
-      <c r="X5" s="14" t="n"/>
-      <c r="Y5" s="14" t="n"/>
-      <c r="Z5" s="14" t="n"/>
-      <c r="AA5" s="14" t="n"/>
-      <c r="AB5" s="14" t="n"/>
-      <c r="AC5" s="14" t="n"/>
-      <c r="AD5" s="14" t="n"/>
-      <c r="AE5" s="14" t="n"/>
-      <c r="AF5" s="14" t="n"/>
-      <c r="AG5" s="14" t="n"/>
-      <c r="AH5" s="14" t="n"/>
+        <f t="shared" ref="D5:AH5" si="0">IF(DATE($C$3,$E$3,1)+COLUMN(D$5)-COLUMN($D$5)&gt;EOMONTH(DATE($C$3,$E$3,1),0),"",DATE($C$3,$E$3,1)+COLUMN(D$5)-COLUMN($D$5))</f>
+        <v/>
+      </c>
+      <c r="E5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="F5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="H5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="I5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="L5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="M5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="O5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Q5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="R5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="S5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="T5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="X5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Z5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AA5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AB5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AC5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AD5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AE5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AF5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AG5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AH5" s="14">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AJ5" s="13" t="inlineStr">
         <is>
           <t>所定日数</t>
@@ -1035,433 +1128,1153 @@
     </row>
     <row r="6">
       <c r="D6" s="15">
-        <f t="array" ref="D6:AH6">IF(D$5:AH$5="","",MID("月火水木金土日",WEEKDAY(D$5:AH$5,2),1))</f>
-        <v/>
-      </c>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
-      <c r="K6" s="15" t="n"/>
-      <c r="L6" s="15" t="n"/>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15" t="n"/>
-      <c r="P6" s="15" t="n"/>
-      <c r="Q6" s="15" t="n"/>
-      <c r="R6" s="15" t="n"/>
-      <c r="S6" s="15" t="n"/>
-      <c r="T6" s="15" t="n"/>
-      <c r="U6" s="15" t="n"/>
-      <c r="V6" s="15" t="n"/>
-      <c r="W6" s="15" t="n"/>
-      <c r="X6" s="15" t="n"/>
-      <c r="Y6" s="15" t="n"/>
-      <c r="Z6" s="15" t="n"/>
-      <c r="AA6" s="15" t="n"/>
-      <c r="AB6" s="15" t="n"/>
-      <c r="AC6" s="15" t="n"/>
-      <c r="AD6" s="15" t="n"/>
-      <c r="AE6" s="15" t="n"/>
-      <c r="AF6" s="15" t="n"/>
-      <c r="AG6" s="15" t="n"/>
-      <c r="AH6" s="15" t="n"/>
+        <f t="shared" ref="D6:AH6" si="1">IF(D$5="","",MID("月火水木金土日",WEEKDAY(D$5,2),1))</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="M6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="O6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="P6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Q6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="R6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="S6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="U6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="V6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="X6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Y6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="Z6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AA6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AB6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AC6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AD6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AE6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AF6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AG6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH6" s="15">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="D7" s="16">
-        <f t="array" ref="D7:AH7">IF(D$5:AH$5="","",IF((HLOOKUP(WEEKDAY(D$5:AH$5,2),BIZ_TABLE,2,0)="×")+(COUNTIF(HOLIDAYS,D$5:AH$5)&gt;0)&gt;0,"休業",""))</f>
-        <v/>
-      </c>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="16" t="n"/>
-      <c r="M7" s="16" t="n"/>
-      <c r="N7" s="16" t="n"/>
-      <c r="O7" s="16" t="n"/>
-      <c r="P7" s="16" t="n"/>
-      <c r="Q7" s="16" t="n"/>
-      <c r="R7" s="16" t="n"/>
-      <c r="S7" s="16" t="n"/>
-      <c r="T7" s="16" t="n"/>
-      <c r="U7" s="16" t="n"/>
-      <c r="V7" s="16" t="n"/>
-      <c r="W7" s="16" t="n"/>
-      <c r="X7" s="16" t="n"/>
-      <c r="Y7" s="16" t="n"/>
-      <c r="Z7" s="16" t="n"/>
-      <c r="AA7" s="16" t="n"/>
-      <c r="AB7" s="16" t="n"/>
-      <c r="AC7" s="16" t="n"/>
-      <c r="AD7" s="16" t="n"/>
-      <c r="AE7" s="16" t="n"/>
-      <c r="AF7" s="16" t="n"/>
-      <c r="AG7" s="16" t="n"/>
-      <c r="AH7" s="16" t="n"/>
+        <f t="shared" ref="D7:AH7" si="2">IF(D$5="","",IF(OR(HLOOKUP(WEEKDAY(D$5,2),BIZ_TABLE,2,0)="×",COUNTIF(HOLIDAYS,D$5)&gt;0),"休業",""))</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="G7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="N7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="P7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Q7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="R7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="S7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="T7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="U7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="V7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="W7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="X7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Y7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="Z7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AA7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AB7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AC7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AD7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AE7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AF7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AG7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="AH7" s="16">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="17">
-        <f t="shared" ref="B8:B13" si="0">IF(設定!B5="","",設定!B5)</f>
+        <f t="shared" ref="B8:B13" si="3">IF(設定!B5="","",設定!B5)</f>
         <v/>
       </c>
       <c r="C8" s="18">
-        <f t="shared" ref="C8:C13" si="1">IF(設定!C5="","",設定!C5)</f>
+        <f t="shared" ref="C8:C13" si="4">IF(設定!C5="","",設定!C5)</f>
         <v/>
       </c>
       <c r="D8" s="19">
-        <f t="array" ref="D8:AH8">IF($B8="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(HLOOKUP(WEEKDAY(D$5:AH$5,2),STAFF_WD,MATCH($B8,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B8&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B8&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")",""))))))</f>
-        <v/>
-      </c>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="19" t="n"/>
-      <c r="H8" s="19" t="n"/>
-      <c r="I8" s="19" t="n"/>
-      <c r="J8" s="19" t="n"/>
-      <c r="K8" s="19" t="n"/>
-      <c r="L8" s="19" t="n"/>
-      <c r="M8" s="19" t="n"/>
-      <c r="N8" s="19" t="n"/>
-      <c r="O8" s="19" t="n"/>
-      <c r="P8" s="19" t="n"/>
-      <c r="Q8" s="19" t="n"/>
-      <c r="R8" s="19" t="n"/>
-      <c r="S8" s="19" t="n"/>
-      <c r="T8" s="19" t="n"/>
-      <c r="U8" s="19" t="n"/>
-      <c r="V8" s="19" t="n"/>
-      <c r="W8" s="19" t="n"/>
-      <c r="X8" s="19" t="n"/>
-      <c r="Y8" s="19" t="n"/>
-      <c r="Z8" s="19" t="n"/>
-      <c r="AA8" s="19" t="n"/>
-      <c r="AB8" s="19" t="n"/>
-      <c r="AC8" s="19" t="n"/>
-      <c r="AD8" s="19" t="n"/>
-      <c r="AE8" s="19" t="n"/>
-      <c r="AF8" s="19" t="n"/>
-      <c r="AG8" s="19" t="n"/>
-      <c r="AH8" s="19" t="n"/>
+        <f t="shared" ref="D8:AH8" si="5">IF(OR($B8="",D$5=""),"",IF(D$7="休業","",IF(HLOOKUP(WEEKDAY(D$5,2),STAFF_WD,MATCH($B8,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B8&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B8&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")","")))))</f>
+        <v/>
+      </c>
+      <c r="E8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="F8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="I8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="K8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="L8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="M8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="N8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Q8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="R8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="S8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="T8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="U8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="V8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="W8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="X8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Y8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Z8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AA8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AB8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AC8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AD8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AE8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AF8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AG8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AH8" s="19">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="AJ8" s="20">
-        <f t="shared" ref="AJ8:AJ13" si="2">IF($B8="","",COUNT(D23:AH23))</f>
+        <f t="shared" ref="AJ8:AJ13" si="6">IF($B8="","",COUNT(D23:AH23))</f>
         <v/>
       </c>
       <c r="AK8" s="21">
-        <f t="shared" ref="AK8:AK13" si="3">IF($B8="","",SUM(D23:AH23))</f>
+        <f t="shared" ref="AK8:AK13" si="7">IF($B8="","",SUM(D23:AH23))</f>
         <v/>
       </c>
       <c r="AL8" s="21">
-        <f t="shared" ref="AL8:AL13" si="4">IF($B8="","",AJ8-AK8)</f>
+        <f t="shared" ref="AL8:AL13" si="8">IF($B8="","",AJ8-AK8)</f>
         <v/>
       </c>
       <c r="AM8" s="21">
-        <f t="shared" ref="AM8:AM13" si="5">IF($B8="","",COUNTIF(D8:AH8,"有")+0.5*(COUNTIF(D8:AH8,"午前")+COUNTIF(D8:AH8,"午後")))</f>
+        <f t="shared" ref="AM8:AM13" si="9">IF($B8="","",COUNTIF(D8:AH8,"有")+0.5*(COUNTIF(D8:AH8,"午前")+COUNTIF(D8:AH8,"午後")))</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C9" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D9" s="19">
-        <f t="array" ref="D9:AH9">IF($B9="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(HLOOKUP(WEEKDAY(D$5:AH$5,2),STAFF_WD,MATCH($B9,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B9&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B9&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")",""))))))</f>
-        <v/>
-      </c>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
-      <c r="H9" s="19" t="n"/>
-      <c r="I9" s="19" t="n"/>
-      <c r="J9" s="19" t="n"/>
-      <c r="K9" s="19" t="n"/>
-      <c r="L9" s="19" t="n"/>
-      <c r="M9" s="19" t="n"/>
-      <c r="N9" s="19" t="n"/>
-      <c r="O9" s="19" t="n"/>
-      <c r="P9" s="19" t="n"/>
-      <c r="Q9" s="19" t="n"/>
-      <c r="R9" s="19" t="n"/>
-      <c r="S9" s="19" t="n"/>
-      <c r="T9" s="19" t="n"/>
-      <c r="U9" s="19" t="n"/>
-      <c r="V9" s="19" t="n"/>
-      <c r="W9" s="19" t="n"/>
-      <c r="X9" s="19" t="n"/>
-      <c r="Y9" s="19" t="n"/>
-      <c r="Z9" s="19" t="n"/>
-      <c r="AA9" s="19" t="n"/>
-      <c r="AB9" s="19" t="n"/>
-      <c r="AC9" s="19" t="n"/>
-      <c r="AD9" s="19" t="n"/>
-      <c r="AE9" s="19" t="n"/>
-      <c r="AF9" s="19" t="n"/>
-      <c r="AG9" s="19" t="n"/>
-      <c r="AH9" s="19" t="n"/>
+        <f t="shared" ref="D9:AH9" si="10">IF(OR($B9="",D$5=""),"",IF(D$7="休業","",IF(HLOOKUP(WEEKDAY(D$5,2),STAFF_WD,MATCH($B9,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B9&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B9&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")","")))))</f>
+        <v/>
+      </c>
+      <c r="E9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="F9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="G9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="I9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="J9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="K9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="L9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="M9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="N9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="O9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Q9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="R9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="S9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="T9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="U9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="V9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="W9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="X9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Y9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="Z9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AA9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AB9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AC9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AD9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AE9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AF9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AG9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AH9" s="19">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ9" s="20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AK9" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AL9" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AM9" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C10" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D10" s="19">
-        <f t="array" ref="D10:AH10">IF($B10="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(HLOOKUP(WEEKDAY(D$5:AH$5,2),STAFF_WD,MATCH($B10,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B10&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B10&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")",""))))))</f>
-        <v/>
-      </c>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
-      <c r="G10" s="19" t="n"/>
-      <c r="H10" s="19" t="n"/>
-      <c r="I10" s="19" t="n"/>
-      <c r="J10" s="19" t="n"/>
-      <c r="K10" s="19" t="n"/>
-      <c r="L10" s="19" t="n"/>
-      <c r="M10" s="19" t="n"/>
-      <c r="N10" s="19" t="n"/>
-      <c r="O10" s="19" t="n"/>
-      <c r="P10" s="19" t="n"/>
-      <c r="Q10" s="19" t="n"/>
-      <c r="R10" s="19" t="n"/>
-      <c r="S10" s="19" t="n"/>
-      <c r="T10" s="19" t="n"/>
-      <c r="U10" s="19" t="n"/>
-      <c r="V10" s="19" t="n"/>
-      <c r="W10" s="19" t="n"/>
-      <c r="X10" s="19" t="n"/>
-      <c r="Y10" s="19" t="n"/>
-      <c r="Z10" s="19" t="n"/>
-      <c r="AA10" s="19" t="n"/>
-      <c r="AB10" s="19" t="n"/>
-      <c r="AC10" s="19" t="n"/>
-      <c r="AD10" s="19" t="n"/>
-      <c r="AE10" s="19" t="n"/>
-      <c r="AF10" s="19" t="n"/>
-      <c r="AG10" s="19" t="n"/>
-      <c r="AH10" s="19" t="n"/>
+        <f t="shared" ref="D10:AH10" si="11">IF(OR($B10="",D$5=""),"",IF(D$7="休業","",IF(HLOOKUP(WEEKDAY(D$5,2),STAFF_WD,MATCH($B10,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B10&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B10&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")","")))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="G10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="H10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="I10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="J10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="L10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="M10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="N10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="O10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="P10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="Q10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="R10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="S10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="T10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="U10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="V10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="W10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="X10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="Y10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="Z10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AA10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AB10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AC10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AD10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AE10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AF10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AG10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AH10" s="19">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="AJ10" s="20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AK10" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AL10" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AM10" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C11" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D11" s="19">
-        <f t="array" ref="D11:AH11">IF($B11="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(HLOOKUP(WEEKDAY(D$5:AH$5,2),STAFF_WD,MATCH($B11,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B11&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B11&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")",""))))))</f>
-        <v/>
-      </c>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="19" t="n"/>
-      <c r="I11" s="19" t="n"/>
-      <c r="J11" s="19" t="n"/>
-      <c r="K11" s="19" t="n"/>
-      <c r="L11" s="19" t="n"/>
-      <c r="M11" s="19" t="n"/>
-      <c r="N11" s="19" t="n"/>
-      <c r="O11" s="19" t="n"/>
-      <c r="P11" s="19" t="n"/>
-      <c r="Q11" s="19" t="n"/>
-      <c r="R11" s="19" t="n"/>
-      <c r="S11" s="19" t="n"/>
-      <c r="T11" s="19" t="n"/>
-      <c r="U11" s="19" t="n"/>
-      <c r="V11" s="19" t="n"/>
-      <c r="W11" s="19" t="n"/>
-      <c r="X11" s="19" t="n"/>
-      <c r="Y11" s="19" t="n"/>
-      <c r="Z11" s="19" t="n"/>
-      <c r="AA11" s="19" t="n"/>
-      <c r="AB11" s="19" t="n"/>
-      <c r="AC11" s="19" t="n"/>
-      <c r="AD11" s="19" t="n"/>
-      <c r="AE11" s="19" t="n"/>
-      <c r="AF11" s="19" t="n"/>
-      <c r="AG11" s="19" t="n"/>
-      <c r="AH11" s="19" t="n"/>
+        <f t="shared" ref="D11:AH11" si="12">IF(OR($B11="",D$5=""),"",IF(D$7="休業","",IF(HLOOKUP(WEEKDAY(D$5,2),STAFF_WD,MATCH($B11,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B11&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B11&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")","")))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="F11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="G11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="H11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="L11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="M11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="N11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="O11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="P11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Q11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="R11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="S11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="T11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="U11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="V11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="W11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Y11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="Z11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AA11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AB11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AC11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AD11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AE11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AF11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AG11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AH11" s="19">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
       <c r="AJ11" s="20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AK11" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AL11" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AM11" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C12" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D12" s="19">
-        <f t="array" ref="D12:AH12">IF($B12="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(HLOOKUP(WEEKDAY(D$5:AH$5,2),STAFF_WD,MATCH($B12,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B12&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B12&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")",""))))))</f>
-        <v/>
-      </c>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="19" t="n"/>
-      <c r="O12" s="19" t="n"/>
-      <c r="P12" s="19" t="n"/>
-      <c r="Q12" s="19" t="n"/>
-      <c r="R12" s="19" t="n"/>
-      <c r="S12" s="19" t="n"/>
-      <c r="T12" s="19" t="n"/>
-      <c r="U12" s="19" t="n"/>
-      <c r="V12" s="19" t="n"/>
-      <c r="W12" s="19" t="n"/>
-      <c r="X12" s="19" t="n"/>
-      <c r="Y12" s="19" t="n"/>
-      <c r="Z12" s="19" t="n"/>
-      <c r="AA12" s="19" t="n"/>
-      <c r="AB12" s="19" t="n"/>
-      <c r="AC12" s="19" t="n"/>
-      <c r="AD12" s="19" t="n"/>
-      <c r="AE12" s="19" t="n"/>
-      <c r="AF12" s="19" t="n"/>
-      <c r="AG12" s="19" t="n"/>
-      <c r="AH12" s="19" t="n"/>
+        <f t="shared" ref="D12:AH12" si="13">IF(OR($B12="",D$5=""),"",IF(D$7="休業","",IF(HLOOKUP(WEEKDAY(D$5,2),STAFF_WD,MATCH($B12,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B12&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B12&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")","")))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="F12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="G12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="H12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="I12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="J12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="L12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="M12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="N12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="O12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="P12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Q12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="R12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="S12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="T12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="U12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="V12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="W12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="X12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Z12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AA12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AB12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AC12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AD12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AE12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AF12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AG12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AH12" s="19">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
       <c r="AJ12" s="20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AK12" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AL12" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AM12" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C13" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="D13" s="19">
-        <f t="array" ref="D13:AH13">IF($B13="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(HLOOKUP(WEEKDAY(D$5:AH$5,2),STAFF_WD,MATCH($B13,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B13&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B13&amp;"|"&amp;TEXT(D$5:AH$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")",""))))))</f>
-        <v/>
-      </c>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="19" t="n"/>
-      <c r="I13" s="19" t="n"/>
-      <c r="J13" s="19" t="n"/>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-      <c r="M13" s="19" t="n"/>
-      <c r="N13" s="19" t="n"/>
-      <c r="O13" s="19" t="n"/>
-      <c r="P13" s="19" t="n"/>
-      <c r="Q13" s="19" t="n"/>
-      <c r="R13" s="19" t="n"/>
-      <c r="S13" s="19" t="n"/>
-      <c r="T13" s="19" t="n"/>
-      <c r="U13" s="19" t="n"/>
-      <c r="V13" s="19" t="n"/>
-      <c r="W13" s="19" t="n"/>
-      <c r="X13" s="19" t="n"/>
-      <c r="Y13" s="19" t="n"/>
-      <c r="Z13" s="19" t="n"/>
-      <c r="AA13" s="19" t="n"/>
-      <c r="AB13" s="19" t="n"/>
-      <c r="AC13" s="19" t="n"/>
-      <c r="AD13" s="19" t="n"/>
-      <c r="AE13" s="19" t="n"/>
-      <c r="AF13" s="19" t="n"/>
-      <c r="AG13" s="19" t="n"/>
-      <c r="AH13" s="19" t="n"/>
+        <f t="shared" ref="D13:AH13" si="14">IF(OR($B13="",D$5=""),"",IF(D$7="休業","",IF(HLOOKUP(WEEKDAY(D$5,2),STAFF_WD,MATCH($B13,STAFF_NAMES,0)+2,0)="×","－",IFERROR(VLOOKUP($B13&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_A,3,0),IFERROR("("&amp;VLOOKUP($B13&amp;"|"&amp;TEXT(D$5,"yyyymmdd"),KEYTAB_P,2,0)&amp;")","")))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="F13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="G13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="H13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="I13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="K13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="L13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="M13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="N13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="O13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="P13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Q13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="R13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="S13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="T13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="U13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="V13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="W13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="X13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Y13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AA13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AB13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AC13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AD13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AE13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AF13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AG13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AH13" s="19">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
       <c r="AJ13" s="20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AK13" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AL13" s="21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AM13" s="21">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -1473,127 +2286,127 @@
       </c>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="23">
-        <f t="shared" ref="D15:AH15" si="6">IF(D$5="","",IF(D$7="休業","－",SUM(D23:D28)))</f>
+        <f t="shared" ref="D15:AH15" si="15">IF(D$5="","",IF(D$7="休業","－",SUM(D23:D28)))</f>
         <v/>
       </c>
       <c r="E15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="F15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="G15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="I15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="L15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="M15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="O15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="P15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="Q15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="R15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="S15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="T15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="U15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="V15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="W15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="X15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="Y15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="Z15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AA15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AB15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AC15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AD15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AE15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AF15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AG15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AH15" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
@@ -1605,127 +2418,127 @@
       </c>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="21">
-        <f t="shared" ref="D16:AH16" si="7">IF(D$5="","",IF(D$7="休業","－",SUMIF($C$8:$C$13,"正社員",D23:D28)))</f>
+        <f t="shared" ref="D16:AH16" si="16">IF(D$5="","",IF(D$7="休業","－",SUMIF($C$8:$C$13,"正社員",D23:D28)))</f>
         <v/>
       </c>
       <c r="E16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="F16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="G16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="M16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="N16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="P16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Q16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="R16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="S16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="T16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="U16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="V16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="W16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="X16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Y16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="Z16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AA16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AB16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AC16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AD16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AE16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AF16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AG16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="AH16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
@@ -1737,127 +2550,127 @@
       </c>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="21">
-        <f t="shared" ref="D17:AH17" si="8">IF(D$5="","",IF(D$7="休業","－",SUMIF($C$8:$C$13,"派遣",D23:D28)))</f>
+        <f t="shared" ref="D17:AH17" si="17">IF(D$5="","",IF(D$7="休業","－",SUMIF($C$8:$C$13,"派遣",D23:D28)))</f>
         <v/>
       </c>
       <c r="E17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="F17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="G17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="I17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="L17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="M17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="O17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="Q17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="R17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="S17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="T17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="U17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="V17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="W17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="X17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="Y17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="Z17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AA17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AB17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AC17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AD17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AF17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AG17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AH17" s="21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -1869,127 +2682,127 @@
       </c>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="25">
-        <f t="shared" ref="D18:AH18" si="9">IF(D$5="","",IF(D$7="休業","－",IF(OR(D15&lt;MIN_ALL,D16&lt;MIN_FT),"NG","OK")))</f>
+        <f t="shared" ref="D18:AH18" si="18">IF(D$5="","",IF(D$7="休業","－",IF(OR(D15&lt;MIN_ALL,D16&lt;MIN_FT),"NG","OK")))</f>
         <v/>
       </c>
       <c r="E18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="F18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="G18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="L18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="M18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="O18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="P18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="Q18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="R18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="S18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="T18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="U18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="V18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="W18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="X18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="Y18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="Z18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AA18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AB18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AC18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AE18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AF18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AG18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AH18" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
@@ -2001,127 +2814,127 @@
       </c>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="21">
-        <f t="shared" ref="D19:AH19" si="10">IF(D$5="","",IF(D$7="休業","－",D15-SUMPRODUCT((LEFT(D8:D13,1)="(")*1)))</f>
+        <f t="shared" ref="D19:AH19" si="19">IF(D$5="","",IF(D$7="休業","－",D15-SUMPRODUCT((LEFT(D8:D13,1)="(")*1)))</f>
         <v/>
       </c>
       <c r="E19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="F19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="G19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="H19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="I19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="L19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="M19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="N19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="O19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="P19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Q19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="R19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="S19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="T19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="U19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="V19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="W19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="X19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Y19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="Z19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AA19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AB19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AC19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AD19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AF19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AG19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AH19" s="21">
-        <f t="shared" si="10"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
@@ -2133,127 +2946,127 @@
       </c>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="25">
-        <f t="shared" ref="D20:AH20" si="11">IF(D$5="","",IF(D$7="休業","－",IF(OR(D19&lt;MIN_ALL,D16-SUMPRODUCT(($C$8:$C$13="正社員")*(LEFT(D8:D13,1)="("))&lt;MIN_FT),"要注意","OK")))</f>
+        <f t="shared" ref="D20:AH20" si="20">IF(D$5="","",IF(D$7="休業","－",IF(OR(D19&lt;MIN_ALL,D16-SUMPRODUCT(($C$8:$C$13="正社員")*(LEFT(D8:D13,1)="("))&lt;MIN_FT),"要注意","OK")))</f>
         <v/>
       </c>
       <c r="E20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="F20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="G20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="I20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="K20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="L20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="M20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="N20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="P20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Q20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="R20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="S20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="T20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="U20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="V20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="W20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="X20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Y20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="Z20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AA20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AB20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AC20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AD20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AE20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AG20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AH20" s="25">
-        <f t="shared" si="11"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
@@ -2266,7 +3079,7 @@
     </row>
     <row r="23">
       <c r="B23" s="27">
-        <f t="shared" ref="B23:B28" si="12">B8</f>
+        <f t="shared" ref="B23:B28" si="21">B8</f>
         <v/>
       </c>
       <c r="C23" s="28" t="inlineStr">
@@ -2275,43 +3088,133 @@
         </is>
       </c>
       <c r="D23" s="29">
-        <f t="array" ref="D23:AH23">IF($B8="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(D8:AH8="－","",IF(D8:AH8="",1,IFERROR(VLOOKUP(D8:AH8,SYM_TBL,3,0),1))))))</f>
-        <v/>
-      </c>
-      <c r="E23" s="29" t="n"/>
-      <c r="F23" s="29" t="n"/>
-      <c r="G23" s="29" t="n"/>
-      <c r="H23" s="29" t="n"/>
-      <c r="I23" s="29" t="n"/>
-      <c r="J23" s="29" t="n"/>
-      <c r="K23" s="29" t="n"/>
-      <c r="L23" s="29" t="n"/>
-      <c r="M23" s="29" t="n"/>
-      <c r="N23" s="29" t="n"/>
-      <c r="O23" s="29" t="n"/>
-      <c r="P23" s="29" t="n"/>
-      <c r="Q23" s="29" t="n"/>
-      <c r="R23" s="29" t="n"/>
-      <c r="S23" s="29" t="n"/>
-      <c r="T23" s="29" t="n"/>
-      <c r="U23" s="29" t="n"/>
-      <c r="V23" s="29" t="n"/>
-      <c r="W23" s="29" t="n"/>
-      <c r="X23" s="29" t="n"/>
-      <c r="Y23" s="29" t="n"/>
-      <c r="Z23" s="29" t="n"/>
-      <c r="AA23" s="29" t="n"/>
-      <c r="AB23" s="29" t="n"/>
-      <c r="AC23" s="29" t="n"/>
-      <c r="AD23" s="29" t="n"/>
-      <c r="AE23" s="29" t="n"/>
-      <c r="AF23" s="29" t="n"/>
-      <c r="AG23" s="29" t="n"/>
-      <c r="AH23" s="29" t="n"/>
+        <f t="shared" ref="D23:AH23" si="22">IF(OR($B8="",D$5="",D$7="休業",D8="－"),"",IF(D8="",1,IFERROR(VLOOKUP(D8,SYM_TBL,3,0),1)))</f>
+        <v/>
+      </c>
+      <c r="E23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="F23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="H23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="I23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="K23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="L23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="M23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="N23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="O23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="P23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Q23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="R23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="S23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="T23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="U23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="V23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="W23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="X23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Y23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="Z23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AA23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AB23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AC23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AD23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AE23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AF23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AG23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AH23" s="29">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="C24" s="28" t="inlineStr">
@@ -2320,43 +3223,133 @@
         </is>
       </c>
       <c r="D24" s="29">
-        <f t="array" ref="D24:AH24">IF($B9="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(D9:AH9="－","",IF(D9:AH9="",1,IFERROR(VLOOKUP(D9:AH9,SYM_TBL,3,0),1))))))</f>
-        <v/>
-      </c>
-      <c r="E24" s="29" t="n"/>
-      <c r="F24" s="29" t="n"/>
-      <c r="G24" s="29" t="n"/>
-      <c r="H24" s="29" t="n"/>
-      <c r="I24" s="29" t="n"/>
-      <c r="J24" s="29" t="n"/>
-      <c r="K24" s="29" t="n"/>
-      <c r="L24" s="29" t="n"/>
-      <c r="M24" s="29" t="n"/>
-      <c r="N24" s="29" t="n"/>
-      <c r="O24" s="29" t="n"/>
-      <c r="P24" s="29" t="n"/>
-      <c r="Q24" s="29" t="n"/>
-      <c r="R24" s="29" t="n"/>
-      <c r="S24" s="29" t="n"/>
-      <c r="T24" s="29" t="n"/>
-      <c r="U24" s="29" t="n"/>
-      <c r="V24" s="29" t="n"/>
-      <c r="W24" s="29" t="n"/>
-      <c r="X24" s="29" t="n"/>
-      <c r="Y24" s="29" t="n"/>
-      <c r="Z24" s="29" t="n"/>
-      <c r="AA24" s="29" t="n"/>
-      <c r="AB24" s="29" t="n"/>
-      <c r="AC24" s="29" t="n"/>
-      <c r="AD24" s="29" t="n"/>
-      <c r="AE24" s="29" t="n"/>
-      <c r="AF24" s="29" t="n"/>
-      <c r="AG24" s="29" t="n"/>
-      <c r="AH24" s="29" t="n"/>
+        <f t="shared" ref="D24:AH24" si="23">IF(OR($B9="",D$5="",D$7="休業",D9="－"),"",IF(D9="",1,IFERROR(VLOOKUP(D9,SYM_TBL,3,0),1)))</f>
+        <v/>
+      </c>
+      <c r="E24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="F24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="G24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="H24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="I24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="J24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="K24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="L24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="M24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="N24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="O24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="P24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="Q24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="R24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="S24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="T24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="U24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="V24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="W24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="X24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="Y24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="Z24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AA24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AB24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AC24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AD24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AE24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AF24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AG24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="AH24" s="29">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="C25" s="28" t="inlineStr">
@@ -2365,43 +3358,133 @@
         </is>
       </c>
       <c r="D25" s="29">
-        <f t="array" ref="D25:AH25">IF($B10="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(D10:AH10="－","",IF(D10:AH10="",1,IFERROR(VLOOKUP(D10:AH10,SYM_TBL,3,0),1))))))</f>
-        <v/>
-      </c>
-      <c r="E25" s="29" t="n"/>
-      <c r="F25" s="29" t="n"/>
-      <c r="G25" s="29" t="n"/>
-      <c r="H25" s="29" t="n"/>
-      <c r="I25" s="29" t="n"/>
-      <c r="J25" s="29" t="n"/>
-      <c r="K25" s="29" t="n"/>
-      <c r="L25" s="29" t="n"/>
-      <c r="M25" s="29" t="n"/>
-      <c r="N25" s="29" t="n"/>
-      <c r="O25" s="29" t="n"/>
-      <c r="P25" s="29" t="n"/>
-      <c r="Q25" s="29" t="n"/>
-      <c r="R25" s="29" t="n"/>
-      <c r="S25" s="29" t="n"/>
-      <c r="T25" s="29" t="n"/>
-      <c r="U25" s="29" t="n"/>
-      <c r="V25" s="29" t="n"/>
-      <c r="W25" s="29" t="n"/>
-      <c r="X25" s="29" t="n"/>
-      <c r="Y25" s="29" t="n"/>
-      <c r="Z25" s="29" t="n"/>
-      <c r="AA25" s="29" t="n"/>
-      <c r="AB25" s="29" t="n"/>
-      <c r="AC25" s="29" t="n"/>
-      <c r="AD25" s="29" t="n"/>
-      <c r="AE25" s="29" t="n"/>
-      <c r="AF25" s="29" t="n"/>
-      <c r="AG25" s="29" t="n"/>
-      <c r="AH25" s="29" t="n"/>
+        <f t="shared" ref="D25:AH25" si="24">IF(OR($B10="",D$5="",D$7="休業",D10="－"),"",IF(D10="",1,IFERROR(VLOOKUP(D10,SYM_TBL,3,0),1)))</f>
+        <v/>
+      </c>
+      <c r="E25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="F25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="H25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="I25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="J25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="L25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="M25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="N25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="O25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="P25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="Q25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="R25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="S25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="T25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="U25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="V25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="W25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="X25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="Y25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="Z25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AA25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AB25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AC25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AD25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AE25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AF25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AG25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AH25" s="29">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="C26" s="28" t="inlineStr">
@@ -2410,43 +3493,133 @@
         </is>
       </c>
       <c r="D26" s="29">
-        <f t="array" ref="D26:AH26">IF($B11="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(D11:AH11="－","",IF(D11:AH11="",1,IFERROR(VLOOKUP(D11:AH11,SYM_TBL,3,0),1))))))</f>
-        <v/>
-      </c>
-      <c r="E26" s="29" t="n"/>
-      <c r="F26" s="29" t="n"/>
-      <c r="G26" s="29" t="n"/>
-      <c r="H26" s="29" t="n"/>
-      <c r="I26" s="29" t="n"/>
-      <c r="J26" s="29" t="n"/>
-      <c r="K26" s="29" t="n"/>
-      <c r="L26" s="29" t="n"/>
-      <c r="M26" s="29" t="n"/>
-      <c r="N26" s="29" t="n"/>
-      <c r="O26" s="29" t="n"/>
-      <c r="P26" s="29" t="n"/>
-      <c r="Q26" s="29" t="n"/>
-      <c r="R26" s="29" t="n"/>
-      <c r="S26" s="29" t="n"/>
-      <c r="T26" s="29" t="n"/>
-      <c r="U26" s="29" t="n"/>
-      <c r="V26" s="29" t="n"/>
-      <c r="W26" s="29" t="n"/>
-      <c r="X26" s="29" t="n"/>
-      <c r="Y26" s="29" t="n"/>
-      <c r="Z26" s="29" t="n"/>
-      <c r="AA26" s="29" t="n"/>
-      <c r="AB26" s="29" t="n"/>
-      <c r="AC26" s="29" t="n"/>
-      <c r="AD26" s="29" t="n"/>
-      <c r="AE26" s="29" t="n"/>
-      <c r="AF26" s="29" t="n"/>
-      <c r="AG26" s="29" t="n"/>
-      <c r="AH26" s="29" t="n"/>
+        <f t="shared" ref="D26:AH26" si="25">IF(OR($B11="",D$5="",D$7="休業",D11="－"),"",IF(D11="",1,IFERROR(VLOOKUP(D11,SYM_TBL,3,0),1)))</f>
+        <v/>
+      </c>
+      <c r="E26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="F26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="G26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="H26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="I26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="J26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="K26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="L26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="M26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="N26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="O26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="P26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="Q26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="R26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="S26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="T26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="U26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="V26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="W26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="X26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="Y26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="Z26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AA26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AB26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AC26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AD26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AE26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AF26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AG26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
+      <c r="AH26" s="29">
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="C27" s="28" t="inlineStr">
@@ -2455,43 +3628,133 @@
         </is>
       </c>
       <c r="D27" s="29">
-        <f t="array" ref="D27:AH27">IF($B12="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(D12:AH12="－","",IF(D12:AH12="",1,IFERROR(VLOOKUP(D12:AH12,SYM_TBL,3,0),1))))))</f>
-        <v/>
-      </c>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="29" t="n"/>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="29" t="n"/>
-      <c r="I27" s="29" t="n"/>
-      <c r="J27" s="29" t="n"/>
-      <c r="K27" s="29" t="n"/>
-      <c r="L27" s="29" t="n"/>
-      <c r="M27" s="29" t="n"/>
-      <c r="N27" s="29" t="n"/>
-      <c r="O27" s="29" t="n"/>
-      <c r="P27" s="29" t="n"/>
-      <c r="Q27" s="29" t="n"/>
-      <c r="R27" s="29" t="n"/>
-      <c r="S27" s="29" t="n"/>
-      <c r="T27" s="29" t="n"/>
-      <c r="U27" s="29" t="n"/>
-      <c r="V27" s="29" t="n"/>
-      <c r="W27" s="29" t="n"/>
-      <c r="X27" s="29" t="n"/>
-      <c r="Y27" s="29" t="n"/>
-      <c r="Z27" s="29" t="n"/>
-      <c r="AA27" s="29" t="n"/>
-      <c r="AB27" s="29" t="n"/>
-      <c r="AC27" s="29" t="n"/>
-      <c r="AD27" s="29" t="n"/>
-      <c r="AE27" s="29" t="n"/>
-      <c r="AF27" s="29" t="n"/>
-      <c r="AG27" s="29" t="n"/>
-      <c r="AH27" s="29" t="n"/>
+        <f t="shared" ref="D27:AH27" si="26">IF(OR($B12="",D$5="",D$7="休業",D12="－"),"",IF(D12="",1,IFERROR(VLOOKUP(D12,SYM_TBL,3,0),1)))</f>
+        <v/>
+      </c>
+      <c r="E27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="F27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="G27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="H27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="I27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="J27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="K27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="L27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="M27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="N27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="O27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="P27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="Q27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="R27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="S27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="T27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="U27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="V27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="W27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="X27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="Y27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="Z27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AA27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AB27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AC27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AD27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AE27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AF27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AG27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AH27" s="29">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="C28" s="28" t="inlineStr">
@@ -2500,39 +3763,129 @@
         </is>
       </c>
       <c r="D28" s="29">
-        <f t="array" ref="D28:AH28">IF($B13="","",IF(D$5:AH$5="","",IF(D$7:AH$7="休業","",IF(D13:AH13="－","",IF(D13:AH13="",1,IFERROR(VLOOKUP(D13:AH13,SYM_TBL,3,0),1))))))</f>
-        <v/>
-      </c>
-      <c r="E28" s="29" t="n"/>
-      <c r="F28" s="29" t="n"/>
-      <c r="G28" s="29" t="n"/>
-      <c r="H28" s="29" t="n"/>
-      <c r="I28" s="29" t="n"/>
-      <c r="J28" s="29" t="n"/>
-      <c r="K28" s="29" t="n"/>
-      <c r="L28" s="29" t="n"/>
-      <c r="M28" s="29" t="n"/>
-      <c r="N28" s="29" t="n"/>
-      <c r="O28" s="29" t="n"/>
-      <c r="P28" s="29" t="n"/>
-      <c r="Q28" s="29" t="n"/>
-      <c r="R28" s="29" t="n"/>
-      <c r="S28" s="29" t="n"/>
-      <c r="T28" s="29" t="n"/>
-      <c r="U28" s="29" t="n"/>
-      <c r="V28" s="29" t="n"/>
-      <c r="W28" s="29" t="n"/>
-      <c r="X28" s="29" t="n"/>
-      <c r="Y28" s="29" t="n"/>
-      <c r="Z28" s="29" t="n"/>
-      <c r="AA28" s="29" t="n"/>
-      <c r="AB28" s="29" t="n"/>
-      <c r="AC28" s="29" t="n"/>
-      <c r="AD28" s="29" t="n"/>
-      <c r="AE28" s="29" t="n"/>
-      <c r="AF28" s="29" t="n"/>
-      <c r="AG28" s="29" t="n"/>
-      <c r="AH28" s="29" t="n"/>
+        <f t="shared" ref="D28:AH28" si="27">IF(OR($B13="",D$5="",D$7="休業",D13="－"),"",IF(D13="",1,IFERROR(VLOOKUP(D13,SYM_TBL,3,0),1)))</f>
+        <v/>
+      </c>
+      <c r="E28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="F28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="G28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="H28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="I28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="J28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="K28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="L28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="M28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="N28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="O28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="P28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="Q28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="R28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="S28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="T28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="U28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="V28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="W28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="X28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="Y28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="Z28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AA28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AB28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AC28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AD28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AE28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AG28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AH28" s="29">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2613,7 +3966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:N8"/>
+  <dimension ref="B1:N124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2642,7 +3995,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1休暇につき1行。連休は日ごとに1行。状態を「承認」にするとシフト表・有給管理に反映される。行の挿入はせず、下に追記する。</t>
+          <t>1休暇につき1行。連休は日ごとに1行。状態を「承認」にするとシフト表・有給管理に反映される。</t>
         </is>
       </c>
     </row>
@@ -2752,28 +4105,28 @@
           <t>正社員B</t>
         </is>
       </c>
-      <c r="I5" s="19">
-        <f t="array" ref="I5:I124">IF(D5:D124="","",COUNTIFS(LOG_DATE,D5:D124,LOG_STATE,"承認")+COUNTIFS(LOG_DATE,D5:D124,LOG_STATE,"申請中")-IF(G5:G124="却下",0,1))</f>
-        <v/>
-      </c>
-      <c r="J5" s="19">
-        <f t="array" ref="J5:J124">IF(D5:D124="","",IFERROR(HLOOKUP(WEEKDAY(D5:D124,2),BIZ_TABLE,3,0)-I5:I124-IF(G5:G124="却下",0,1),"日付を確認"))</f>
-        <v/>
-      </c>
-      <c r="K5" s="33">
-        <f t="array" ref="K5:K124">IF(D5:D124="","",IFERROR(IF((HLOOKUP(WEEKDAY(D5:D124,2),BIZ_TABLE,2,0)="×")+(COUNTIF(HOLIDAYS,D5:D124)&gt;0)&gt;0,"休業日",IF(J5:J124&lt;MIN_ALL,"要確認","OK")),"日付を確認"))</f>
-        <v/>
-      </c>
-      <c r="L5" s="34">
-        <f t="array" ref="L5:L124">IF((G5:G124="承認")*(C5:C124&lt;&gt;"")*(D5:D124&lt;&gt;""),C5:C124&amp;"|"&amp;TEXT(D5:D124,"yyyymmdd"),"")</f>
-        <v/>
-      </c>
-      <c r="M5" s="34">
-        <f t="array" ref="M5:M124">IF((G5:G124="申請中")*(C5:C124&lt;&gt;"")*(D5:D124&lt;&gt;""),C5:C124&amp;"|"&amp;TEXT(D5:D124,"yyyymmdd"),"")</f>
-        <v/>
-      </c>
-      <c r="N5" s="34">
-        <f t="array" ref="N5:N124">IF(E5:E124="","",E5:E124)</f>
+      <c r="I5" s="33">
+        <f t="shared" ref="I5:I124" si="0">IF(D5="","",COUNTIFS(LOG_DATE,D5,LOG_STATE,"承認")+COUNTIFS(LOG_DATE,D5,LOG_STATE,"申請中")-IF(G5="却下",0,1))</f>
+        <v/>
+      </c>
+      <c r="J5" s="33">
+        <f t="shared" ref="J5:J124" si="1">IF(D5="","",IFERROR(HLOOKUP(WEEKDAY(D5,2),BIZ_TABLE,3,0)-I5-IF(G5="却下",0,1),"日付を確認"))</f>
+        <v/>
+      </c>
+      <c r="K5" s="34">
+        <f t="shared" ref="K5:K124" si="2">IF(D5="","",IFERROR(IF(OR(HLOOKUP(WEEKDAY(D5,2),BIZ_TABLE,2,0)="×",COUNTIF(HOLIDAYS,D5)&gt;0),"休業日",IF(J5&lt;MIN_ALL,"要確認","OK")),"日付を確認"))</f>
+        <v/>
+      </c>
+      <c r="L5" s="35">
+        <f t="shared" ref="L5:L124" si="3">IF(AND(G5="承認",C5&lt;&gt;"",D5&lt;&gt;""),C5&amp;"|"&amp;TEXT(D5,"yyyymmdd"),"")</f>
+        <v/>
+      </c>
+      <c r="M5" s="35">
+        <f t="shared" ref="M5:M124" si="4">IF(AND(G5="申請中",C5&lt;&gt;"",D5&lt;&gt;""),C5&amp;"|"&amp;TEXT(D5,"yyyymmdd"),"")</f>
+        <v/>
+      </c>
+      <c r="N5" s="35">
+        <f t="shared" ref="N5:N124" si="5">IF(E5="","",E5)</f>
         <v/>
       </c>
     </row>
@@ -2805,6 +4158,30 @@
         </is>
       </c>
       <c r="H6" s="31" t="n"/>
+      <c r="I6" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J6" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K6" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L6" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M6" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N6" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="30" t="n">
@@ -2838,6 +4215,30 @@
           <t>正社員A</t>
         </is>
       </c>
+      <c r="I7" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J7" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K7" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L7" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M7" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N7" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="30" t="n">
@@ -2867,6 +4268,3046 @@
         </is>
       </c>
       <c r="H8" s="31" t="n"/>
+      <c r="I8" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J8" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K8" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L8" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M8" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N8" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="I9" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J9" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K9" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L9" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M9" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N9" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="I10" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J10" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K10" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L10" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M10" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N10" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="I11" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J11" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K11" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L11" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M11" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N11" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="I12" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J12" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K12" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L12" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M12" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N12" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="I13" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J13" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K13" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L13" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M13" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N13" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="I14" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J14" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K14" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L14" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M14" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N14" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="I15" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J15" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K15" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L15" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M15" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N15" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="I16" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J16" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K16" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L16" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M16" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N16" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="I17" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J17" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K17" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L17" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M17" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N17" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="I18" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J18" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K18" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L18" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M18" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N18" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="I19" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J19" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K19" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L19" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M19" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N19" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="I20" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J20" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K20" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L20" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M20" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N20" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="I21" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J21" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K21" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L21" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M21" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N21" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="I22" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J22" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K22" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L22" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M22" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N22" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="I23" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J23" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K23" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L23" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M23" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N23" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="I24" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J24" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K24" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L24" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M24" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N24" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="I25" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J25" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K25" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L25" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M25" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N25" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="I26" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J26" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K26" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L26" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M26" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N26" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="I27" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J27" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K27" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L27" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M27" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N27" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="I28" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J28" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K28" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L28" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M28" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N28" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="I29" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J29" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K29" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L29" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M29" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N29" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="I30" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J30" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K30" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L30" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M30" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N30" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="I31" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J31" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K31" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L31" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M31" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N31" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="I32" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J32" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K32" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L32" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M32" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N32" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="I33" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J33" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K33" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L33" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M33" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N33" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="I34" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J34" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K34" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L34" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M34" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N34" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="I35" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J35" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K35" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L35" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M35" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N35" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="I36" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J36" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K36" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L36" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M36" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N36" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="I37" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J37" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K37" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L37" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M37" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N37" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="I38" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J38" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K38" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L38" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M38" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N38" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="I39" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J39" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K39" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L39" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M39" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N39" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="I40" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J40" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K40" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L40" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M40" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N40" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="I41" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J41" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K41" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L41" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M41" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N41" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="I42" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J42" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K42" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L42" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M42" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N42" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="I43" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J43" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K43" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L43" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M43" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N43" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="I44" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J44" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K44" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L44" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M44" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N44" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="I45" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J45" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K45" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L45" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M45" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N45" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="I46" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J46" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K46" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L46" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M46" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N46" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="I47" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J47" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K47" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L47" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M47" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N47" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="I48" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J48" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K48" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L48" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M48" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N48" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="I49" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J49" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K49" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L49" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M49" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N49" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="I50" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J50" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K50" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L50" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M50" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N50" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="I51" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J51" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K51" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L51" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M51" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N51" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="I52" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J52" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K52" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L52" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M52" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N52" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="I53" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J53" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K53" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L53" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M53" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N53" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="I54" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J54" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K54" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L54" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M54" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N54" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="I55" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J55" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K55" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L55" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M55" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N55" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="I56" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J56" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K56" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L56" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M56" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N56" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="I57" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J57" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K57" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L57" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M57" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N57" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="I58" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J58" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K58" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L58" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M58" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N58" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="I59" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J59" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K59" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L59" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M59" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N59" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="I60" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J60" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K60" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L60" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M60" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N60" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="I61" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J61" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K61" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L61" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M61" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N61" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="I62" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J62" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K62" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L62" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M62" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N62" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="I63" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J63" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K63" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L63" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M63" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N63" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="I64" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J64" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K64" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L64" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M64" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N64" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="I65" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J65" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K65" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L65" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M65" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N65" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="I66" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J66" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K66" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L66" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M66" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N66" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="I67" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J67" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K67" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L67" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M67" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N67" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="I68" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J68" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K68" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L68" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M68" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N68" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="I69" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J69" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K69" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L69" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M69" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N69" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="I70" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J70" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K70" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L70" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M70" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N70" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="I71" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J71" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K71" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L71" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M71" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N71" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="I72" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J72" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K72" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L72" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M72" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N72" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="I73" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J73" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K73" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L73" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M73" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N73" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="I74" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J74" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K74" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L74" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M74" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N74" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="I75" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J75" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K75" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L75" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M75" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N75" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="I76" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J76" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K76" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L76" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M76" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N76" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="I77" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J77" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K77" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L77" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M77" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N77" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="I78" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J78" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K78" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L78" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M78" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N78" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="I79" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J79" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K79" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L79" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M79" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N79" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="I80" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J80" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K80" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L80" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M80" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N80" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="I81" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J81" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K81" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L81" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M81" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N81" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="I82" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J82" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K82" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L82" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M82" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N82" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="I83" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J83" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K83" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L83" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M83" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N83" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="I84" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J84" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K84" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L84" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M84" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N84" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="I85" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J85" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K85" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L85" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M85" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N85" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="I86" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J86" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K86" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L86" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M86" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N86" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="I87" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J87" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K87" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L87" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M87" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N87" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="I88" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J88" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K88" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L88" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M88" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N88" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="I89" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J89" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K89" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L89" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M89" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N89" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="I90" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J90" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K90" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L90" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M90" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N90" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="I91" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J91" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K91" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L91" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M91" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N91" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="I92" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J92" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K92" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L92" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M92" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N92" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="I93" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J93" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K93" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L93" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M93" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N93" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="I94" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J94" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K94" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L94" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M94" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N94" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="I95" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J95" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K95" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L95" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M95" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N95" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="I96" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J96" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K96" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L96" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M96" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N96" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="I97" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J97" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K97" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L97" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M97" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N97" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="I98" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J98" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K98" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L98" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M98" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N98" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="I99" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J99" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K99" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L99" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M99" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N99" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="I100" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J100" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K100" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L100" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M100" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N100" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="I101" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J101" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K101" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L101" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M101" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N101" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="I102" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J102" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K102" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L102" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M102" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N102" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="I103" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J103" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K103" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L103" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M103" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N103" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="I104" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J104" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K104" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L104" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M104" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N104" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="I105" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J105" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K105" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L105" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M105" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N105" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="I106" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J106" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K106" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L106" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M106" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N106" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="I107" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J107" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K107" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L107" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M107" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N107" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="I108" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J108" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K108" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L108" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M108" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N108" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="I109" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J109" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K109" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L109" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M109" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N109" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="I110" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J110" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K110" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L110" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M110" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N110" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="I111" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J111" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K111" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L111" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M111" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N111" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="I112" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J112" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K112" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L112" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M112" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N112" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="I113" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J113" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K113" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L113" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M113" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N113" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="I114" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J114" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K114" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L114" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M114" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N114" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="I115" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J115" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K115" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L115" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M115" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N115" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="I116" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J116" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K116" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L116" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M116" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N116" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="I117" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J117" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K117" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L117" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M117" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N117" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="I118" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J118" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K118" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L118" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M118" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N118" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="I119" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J119" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K119" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L119" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M119" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N119" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="I120" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J120" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K120" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L120" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M120" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N120" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="I121" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J121" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K121" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L121" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M121" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N121" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="I122" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J122" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K122" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L122" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M122" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N122" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="I123" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J123" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K123" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L123" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M123" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N123" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="I124" s="33">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J124" s="33">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K124" s="34">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L124" s="35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M124" s="35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N124" s="35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:H124">
@@ -3014,13 +7455,13 @@
         <f t="shared" ref="C5:C10" si="1">IF(設定!C5="","",設定!C5)</f>
         <v/>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="36" t="n">
         <v>46113</v>
       </c>
-      <c r="E5" s="36" t="n">
+      <c r="E5" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="37" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="21">
@@ -3035,7 +7476,7 @@
         <f t="shared" ref="I5:I10" si="4">IF(B5="","",IF(C5="派遣","対象外（派遣元）",IF(E5&gt;=10,IF(G5&gt;=5,"達成","あと"&amp;(5-G5)&amp;"日"),"対象外")))</f>
         <v/>
       </c>
-      <c r="J5" s="37" t="inlineStr">
+      <c r="J5" s="38" t="inlineStr">
         <is>
           <t>付与日数・繰越は例。実際の値に直す</t>
         </is>
@@ -3050,13 +7491,13 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="36" t="n">
         <v>46113</v>
       </c>
-      <c r="E6" s="36" t="n">
+      <c r="E6" s="37" t="n">
         <v>11</v>
       </c>
-      <c r="F6" s="36" t="n">
+      <c r="F6" s="37" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="21">
@@ -3071,7 +7512,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J6" s="37" t="n"/>
+      <c r="J6" s="38" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="17">
@@ -3082,9 +7523,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="37" t="n"/>
       <c r="G7" s="21">
         <f t="shared" si="2"/>
         <v/>
@@ -3097,7 +7538,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J7" s="37" t="n"/>
+      <c r="J7" s="38" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="17">
@@ -3108,9 +7549,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="37" t="n"/>
       <c r="G8" s="21">
         <f t="shared" si="2"/>
         <v/>
@@ -3123,7 +7564,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J8" s="37" t="n"/>
+      <c r="J8" s="38" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="17">
@@ -3134,9 +7575,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="36" t="n"/>
-      <c r="F9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="37" t="n"/>
       <c r="G9" s="21">
         <f t="shared" si="2"/>
         <v/>
@@ -3149,7 +7590,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J9" s="37" t="n"/>
+      <c r="J9" s="38" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="17">
@@ -3160,9 +7601,9 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="36" t="n"/>
-      <c r="F10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="37" t="n"/>
       <c r="G10" s="21">
         <f t="shared" si="2"/>
         <v/>
@@ -3175,7 +7616,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="J10" s="37" t="n"/>
+      <c r="J10" s="38" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I5:I10">
@@ -3228,37 +7669,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="38" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>メンバー（氏名・区分・勤務曜日 ○×）</t>
         </is>
       </c>
-      <c r="N2" s="38" t="inlineStr">
+      <c r="N2" s="39" t="inlineStr">
         <is>
           <t>祝日・会社休業日（追加可）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="39" t="n">
+      <c r="D3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="39" t="n">
+      <c r="E3" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="39" t="n">
+      <c r="F3" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="39" t="n">
+      <c r="G3" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="39" t="n">
+      <c r="H3" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="I3" s="39" t="n">
+      <c r="I3" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="39" t="n">
+      <c r="J3" s="40" t="n">
         <v>7</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -3330,52 +7771,52 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>正社員A</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C5" s="42" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E5" s="41" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F5" s="41" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G5" s="41" t="inlineStr">
+      <c r="G5" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H5" s="41" t="inlineStr">
+      <c r="H5" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I5" s="41" t="inlineStr">
+      <c r="I5" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J5" s="41" t="inlineStr">
+      <c r="J5" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="K5" s="37" t="inlineStr">
+      <c r="K5" s="38" t="inlineStr">
         <is>
           <t>氏名を実名に書き換える</t>
         </is>
@@ -3390,52 +7831,52 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>正社員B</t>
         </is>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t>正社員</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E6" s="41" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="41" t="inlineStr">
+      <c r="F6" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G6" s="41" t="inlineStr">
+      <c r="G6" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H6" s="41" t="inlineStr">
+      <c r="H6" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I6" s="41" t="inlineStr">
+      <c r="I6" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J6" s="41" t="inlineStr">
+      <c r="J6" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="K6" s="37" t="n"/>
+      <c r="K6" s="38" t="n"/>
       <c r="N6" s="30" t="n">
         <v>46287</v>
       </c>
@@ -3446,52 +7887,52 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>派遣A</t>
         </is>
       </c>
-      <c r="C7" s="41" t="inlineStr">
+      <c r="C7" s="42" t="inlineStr">
         <is>
           <t>派遣</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E7" s="41" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="F7" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G7" s="41" t="inlineStr">
+      <c r="G7" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H7" s="41" t="inlineStr">
+      <c r="H7" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I7" s="41" t="inlineStr">
+      <c r="I7" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J7" s="41" t="inlineStr">
+      <c r="J7" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="K7" s="37" t="inlineStr">
+      <c r="K7" s="38" t="inlineStr">
         <is>
           <t>契約の勤務曜日に合わせて○×を直す</t>
         </is>
@@ -3506,52 +7947,52 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>派遣B</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>派遣</t>
         </is>
       </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E8" s="41" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F8" s="41" t="inlineStr">
+      <c r="F8" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G8" s="41" t="inlineStr">
+      <c r="G8" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H8" s="41" t="inlineStr">
+      <c r="H8" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I8" s="41" t="inlineStr">
+      <c r="I8" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J8" s="41" t="inlineStr">
+      <c r="J8" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="K8" s="37" t="n"/>
+      <c r="K8" s="38" t="n"/>
       <c r="N8" s="30" t="n">
         <v>46307</v>
       </c>
@@ -3562,44 +8003,44 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="40" t="inlineStr"/>
-      <c r="C9" s="41" t="inlineStr"/>
-      <c r="D9" s="41" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr"/>
+      <c r="C9" s="42" t="inlineStr"/>
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="E9" s="41" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="F9" s="41" t="inlineStr">
+      <c r="F9" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G9" s="41" t="inlineStr">
+      <c r="G9" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H9" s="41" t="inlineStr">
+      <c r="H9" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="I9" s="41" t="inlineStr">
+      <c r="I9" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J9" s="41" t="inlineStr">
+      <c r="J9" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="K9" s="37" t="inlineStr">
+      <c r="K9" s="38" t="inlineStr">
         <is>
           <t>増員したらここに追加</t>
         </is>
@@ -3614,44 +8055,44 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="40" t="inlineStr"/>
-      <c r="C10" s="41" t="inlineStr"/>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr"/>
+      <c r="C10" s="42" t="inlineStr"/>
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="F10" s="41" t="inlineStr">
+      <c r="F10" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="G10" s="41" t="inlineStr">
+      <c r="G10" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="H10" s="41" t="inlineStr">
+      <c r="H10" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="I10" s="41" t="inlineStr">
+      <c r="I10" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J10" s="41" t="inlineStr">
+      <c r="J10" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="K10" s="37" t="n"/>
+      <c r="K10" s="38" t="n"/>
       <c r="N10" s="30" t="n">
         <v>46349</v>
       </c>
@@ -3672,7 +8113,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>営業曜日（×の曜日は休業日。祝日は右の一覧で指定）</t>
         </is>
@@ -3738,31 +8179,31 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t>曜日番号</t>
         </is>
       </c>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="43" t="n">
+      <c r="E14" s="44" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="43" t="n">
+      <c r="F14" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="43" t="n">
+      <c r="G14" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="43" t="n">
+      <c r="H14" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="I14" s="43" t="n">
+      <c r="I14" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="43" t="n">
+      <c r="J14" s="44" t="n">
         <v>7</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -3781,37 +8222,37 @@
         </is>
       </c>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="41" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="E15" s="41" t="inlineStr">
+      <c r="E15" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F15" s="41" t="inlineStr">
+      <c r="F15" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="G15" s="41" t="inlineStr">
+      <c r="G15" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H15" s="41" t="inlineStr">
+      <c r="H15" s="42" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="I15" s="41" t="inlineStr">
+      <c r="I15" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
       </c>
-      <c r="J15" s="41" t="inlineStr">
+      <c r="J15" s="42" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -3826,7 +8267,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>勤務予定人数（自動）</t>
         </is>
@@ -3880,7 +8321,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>ルール（人数の下限）</t>
         </is>
@@ -3895,12 +8336,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="45" t="inlineStr">
         <is>
           <t>最低出勤人数（1日あたり）</t>
         </is>
       </c>
-      <c r="C19" s="41" t="n">
+      <c r="C19" s="42" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="26" t="inlineStr">
@@ -3918,12 +8359,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>最低正社員出勤人数</t>
         </is>
       </c>
-      <c r="C20" s="41" t="n">
+      <c r="C20" s="42" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="26" t="inlineStr">
@@ -3941,12 +8382,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="45" t="inlineStr">
         <is>
           <t>申請期限の目安</t>
         </is>
       </c>
-      <c r="C21" s="40" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>休みたい日の1週間前まで</t>
         </is>
@@ -3979,7 +8420,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t>記号（休暇申請の種別）　出勤係数: 1=出勤 / 0=休み / 0.5=半日</t>
         </is>
@@ -4024,21 +8465,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="45" t="inlineStr">
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
-      <c r="C25" s="44" t="inlineStr">
+      <c r="C25" s="45" t="inlineStr">
         <is>
           <t>有給休暇</t>
         </is>
       </c>
-      <c r="D25" s="46" t="n">
+      <c r="D25" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="5" t="n"/>
-      <c r="F25" s="47" t="inlineStr">
+      <c r="F25" s="48" t="inlineStr">
         <is>
           <t>正社員は年5日取得義務の対象</t>
         </is>
@@ -4058,21 +8499,21 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="45" t="inlineStr">
+      <c r="B26" s="46" t="inlineStr">
         <is>
           <t>午前</t>
         </is>
       </c>
-      <c r="C26" s="44" t="inlineStr">
+      <c r="C26" s="45" t="inlineStr">
         <is>
           <t>午前半休</t>
         </is>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="47" t="n">
         <v>0.5</v>
       </c>
       <c r="E26" s="5" t="n"/>
-      <c r="F26" s="47" t="inlineStr">
+      <c r="F26" s="48" t="inlineStr">
         <is>
           <t>0.5日の有給として集計</t>
         </is>
@@ -4092,21 +8533,21 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="45" t="inlineStr">
+      <c r="B27" s="46" t="inlineStr">
         <is>
           <t>午後</t>
         </is>
       </c>
-      <c r="C27" s="44" t="inlineStr">
+      <c r="C27" s="45" t="inlineStr">
         <is>
           <t>午後半休</t>
         </is>
       </c>
-      <c r="D27" s="46" t="n">
+      <c r="D27" s="47" t="n">
         <v>0.5</v>
       </c>
       <c r="E27" s="5" t="n"/>
-      <c r="F27" s="47" t="inlineStr">
+      <c r="F27" s="48" t="inlineStr">
         <is>
           <t>0.5日の有給として集計</t>
         </is>
@@ -4126,21 +8567,21 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="45" t="inlineStr">
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t>休</t>
         </is>
       </c>
-      <c r="C28" s="44" t="inlineStr">
+      <c r="C28" s="45" t="inlineStr">
         <is>
           <t>公休・希望休</t>
         </is>
       </c>
-      <c r="D28" s="46" t="n">
+      <c r="D28" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="5" t="n"/>
-      <c r="F28" s="47" t="inlineStr">
+      <c r="F28" s="48" t="inlineStr">
         <is>
           <t>無給の休み・シフト調整による休み</t>
         </is>
@@ -4160,21 +8601,21 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="45" t="inlineStr">
+      <c r="B29" s="46" t="inlineStr">
         <is>
           <t>特</t>
         </is>
       </c>
-      <c r="C29" s="44" t="inlineStr">
+      <c r="C29" s="45" t="inlineStr">
         <is>
           <t>特別休暇（慶弔など）</t>
         </is>
       </c>
-      <c r="D29" s="46" t="n">
+      <c r="D29" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="5" t="n"/>
-      <c r="F29" s="47" t="n"/>
+      <c r="F29" s="48" t="n"/>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
@@ -4190,21 +8631,21 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="45" t="inlineStr">
+      <c r="B30" s="46" t="inlineStr">
         <is>
           <t>代</t>
         </is>
       </c>
-      <c r="C30" s="44" t="inlineStr">
+      <c r="C30" s="45" t="inlineStr">
         <is>
           <t>代休・振替休日</t>
         </is>
       </c>
-      <c r="D30" s="46" t="n">
+      <c r="D30" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="5" t="n"/>
-      <c r="F30" s="47" t="n"/>
+      <c r="F30" s="48" t="n"/>
       <c r="G30" s="6" t="n"/>
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="n"/>
@@ -4220,21 +8661,21 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="45" t="inlineStr">
+      <c r="B31" s="46" t="inlineStr">
         <is>
           <t>欠</t>
         </is>
       </c>
-      <c r="C31" s="44" t="inlineStr">
+      <c r="C31" s="45" t="inlineStr">
         <is>
           <t>欠勤</t>
         </is>
       </c>
-      <c r="D31" s="46" t="n">
+      <c r="D31" s="47" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="5" t="n"/>
-      <c r="F31" s="47" t="inlineStr">
+      <c r="F31" s="48" t="inlineStr">
         <is>
           <t>事後登録用</t>
         </is>
@@ -4254,21 +8695,21 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="45" t="inlineStr">
+      <c r="B32" s="46" t="inlineStr">
         <is>
           <t>在</t>
         </is>
       </c>
-      <c r="C32" s="44" t="inlineStr">
+      <c r="C32" s="45" t="inlineStr">
         <is>
           <t>在宅勤務</t>
         </is>
       </c>
-      <c r="D32" s="46" t="n">
+      <c r="D32" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="5" t="n"/>
-      <c r="F32" s="47" t="inlineStr">
+      <c r="F32" s="48" t="inlineStr">
         <is>
           <t>出勤扱い。所在把握のために記録</t>
         </is>
@@ -4280,21 +8721,21 @@
       <c r="K32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="46" t="inlineStr">
         <is>
           <t>外</t>
         </is>
       </c>
-      <c r="C33" s="44" t="inlineStr">
+      <c r="C33" s="45" t="inlineStr">
         <is>
           <t>外出・出張</t>
         </is>
       </c>
-      <c r="D33" s="46" t="n">
+      <c r="D33" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="5" t="n"/>
-      <c r="F33" s="47" t="inlineStr">
+      <c r="F33" s="48" t="inlineStr">
         <is>
           <t>出勤扱い。事務所が無人になる場合は別途注意</t>
         </is>
@@ -4379,181 +8820,181 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="48" t="n"/>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="B4" s="49" t="n"/>
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>■ 基本の考え方</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="50" t="inlineStr">
-        <is>
-          <t>・入力するのは「休暇申請」シートだけ。1休暇につき1行（連休は日ごとに1行）。行の挿入はせず下に追記する。</t>
+      <c r="C5" s="51" t="inlineStr">
+        <is>
+          <t>・入力するのは「休暇申請」シートだけ。1休暇につき1行（連休は日ごとに1行）。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="50" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>・「シフト表」は年・月を切り替えるだけで自動で組み上がる。「有給管理」は承認済みの申請から自動集計。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="50" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
         <is>
           <t>・黄色のセル = 入力する場所。灰色のセル = 自動計算（触らない）。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="48" t="n"/>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="B8" s="49" t="n"/>
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>■ 最初にやること（5分）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="50" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>1. 「設定」でメンバー4名の氏名・区分（正社員／派遣）・勤務曜日（○×）を入れる。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="50" t="inlineStr">
+      <c r="C10" s="51" t="inlineStr">
         <is>
           <t>2. 「設定」の最低出勤人数（初期値 2名）と最低正社員出勤人数（初期値 1名）を確認する。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="50" t="inlineStr">
+      <c r="C11" s="51" t="inlineStr">
         <is>
           <t>3. 「有給管理」に各人の付与日・付与日数・繰越を入れる（派遣の残数は派遣元管理なので不要）。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="50" t="inlineStr">
+      <c r="C12" s="51" t="inlineStr">
         <is>
           <t>4. サンプルの申請4行（9/10に3人が重なって「要確認」が出る例）は削除してよい。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="48" t="n"/>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="B13" s="49" t="n"/>
+      <c r="C13" s="50" t="inlineStr">
         <is>
           <t>■ 休みを取りたいとき（申請者）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="50" t="inlineStr">
+      <c r="C14" s="51" t="inlineStr">
         <is>
           <t>1. 「休暇申請」に申請日・氏名・休暇日・種別・理由を1行追加。状態は「申請中」。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="50" t="inlineStr">
+      <c r="C15" s="51" t="inlineStr">
         <is>
           <t>2. 「判定」列に「要確認」と出たら、その日は既に誰かが休む予定。日程をずらせないか先に相談する。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="48" t="n"/>
-      <c r="C16" s="49" t="inlineStr">
+      <c r="B16" s="49" t="n"/>
+      <c r="C16" s="50" t="inlineStr">
         <is>
           <t>■ 承認するとき（管理者）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="50" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
         <is>
           <t>1. 「シフト表」の「申請中を承認した場合の判定」行が「要注意」なら、承認すると最低人数を割る。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="50" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>2. 問題なければ状態を「承認」に変え、承認者名を入れる。却下なら「却下」。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="50" t="inlineStr">
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>3. 派遣メンバーの休みは、承認と同時に派遣元（派遣会社）にも連絡する。派遣元にとって勤怠実績は請求根拠。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="48" t="n"/>
-      <c r="C20" s="49" t="inlineStr">
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="50" t="inlineStr">
         <is>
           <t>■ 運用ルールの例</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="50" t="inlineStr">
+      <c r="C21" s="51" t="inlineStr">
         <is>
           <t>・申請は原則、休みたい日の1週間前まで。急な体調不良は当日連絡＋事後に「欠」または「有」で登録。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="50" t="inlineStr">
+      <c r="C22" s="51" t="inlineStr">
         <is>
           <t>・同じ日に希望が重なったら「先に申請した人」より「直近3か月の休み取得が少ない人」を優先すると不公平感が出にくい。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="50" t="inlineStr">
+      <c r="C23" s="51" t="inlineStr">
         <is>
           <t>・派遣2名だけの出勤日は作らない（指揮命令者が不在になる）。最低正社員出勤人数=1 はそのための設定。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="50" t="inlineStr">
+      <c r="C24" s="51" t="inlineStr">
         <is>
           <t>・正社員は年5日の有給取得義務あり。「年5日義務」列が「あと○日」のままなら管理者側から取得日を提案する。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="48" t="n"/>
-      <c r="C25" s="49" t="inlineStr">
+      <c r="B25" s="49" t="n"/>
+      <c r="C25" s="50" t="inlineStr">
         <is>
           <t>■ 注意</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="50" t="inlineStr">
+      <c r="C26" s="51" t="inlineStr">
         <is>
           <t>・休暇申請の日付は必ず日付形式（2026/9/10）で入力。文字として入ると集計に乗らない。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="50" t="inlineStr">
-        <is>
-          <t>・自動列は120行分。超える場合は「休暇申請」の各自動列の数式の範囲（5:124）を広げる。</t>
+      <c r="C27" s="51" t="inlineStr">
+        <is>
+          <t>・自動列は120行分。超える場合は「休暇申請」の最終行をコピーして下に貼り付ける。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="50" t="inlineStr">
+      <c r="C28" s="51" t="inlineStr">
         <is>
           <t>・半休は「同日の他の休み」「申請中の判定」では1人分の休みとして数える（安全側）。承認後の出勤人数は0.5で数える。</t>
         </is>
